--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Brads Towing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F61B1A1-3341-4B5A-B24F-6ECF83F42691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21203CC4-AB9B-4212-9BAF-7D17244241F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="1065" windowWidth="24720" windowHeight="14235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Brads Towing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21203CC4-AB9B-4212-9BAF-7D17244241F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7239A97D-AE14-43F1-ADF8-655D9CF55C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7239A97D-AE14-43F1-ADF8-655D9CF55C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F2AEB4-C676-4532-876A-393928390889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F2AEB4-C676-4532-876A-393928390889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0F15F2-D2F3-4665-8AEA-0A4AFFB1AB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0F15F2-D2F3-4665-8AEA-0A4AFFB1AB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9AAA45-F9BD-4919-A7C2-2A578528C60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9AAA45-F9BD-4919-A7C2-2A578528C60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF6C2D6-1B75-47F2-AF4E-91184D941B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF6C2D6-1B75-47F2-AF4E-91184D941B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52299CDF-2CA7-46DD-BFBE-610E2F994C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="26">
   <si>
     <t>Company Name</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Joe Riley</t>
+  </si>
+  <si>
+    <t>Rules for Safe Driving</t>
   </si>
 </sst>
 </file>
@@ -969,16 +972,91 @@
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H20" s="2"/>
-      <c r="I20" s="1"/>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>4962</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>46146.647569444445</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H21" s="2"/>
-      <c r="I21" s="1"/>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>4965</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>46146.648263888892</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H22" s="2"/>
-      <c r="I22" s="1"/>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <v>4963</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>46146.648958333331</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H23" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52299CDF-2CA7-46DD-BFBE-610E2F994C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBB7A14-55A2-4D45-8ADE-B923D5A6625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="45">
   <si>
     <t>Company Name</t>
   </si>
@@ -117,6 +117,63 @@
   </si>
   <si>
     <t>Rules for Safe Driving</t>
+  </si>
+  <si>
+    <t>Austin Simms</t>
+  </si>
+  <si>
+    <t>Bailey Bulyar</t>
+  </si>
+  <si>
+    <t>Bruce Willard</t>
+  </si>
+  <si>
+    <t>Cory Volland</t>
+  </si>
+  <si>
+    <t>Damien Strahl</t>
+  </si>
+  <si>
+    <t>Dominic Moore</t>
+  </si>
+  <si>
+    <t>Garrett Jackman</t>
+  </si>
+  <si>
+    <t>JD Chappell</t>
+  </si>
+  <si>
+    <t>Joe Cruz</t>
+  </si>
+  <si>
+    <t>Joey Bybee</t>
+  </si>
+  <si>
+    <t>John Sandstrom</t>
+  </si>
+  <si>
+    <t>Kenny Mayfield</t>
+  </si>
+  <si>
+    <t>Manny Rodenberg</t>
+  </si>
+  <si>
+    <t>Marcus Trimble</t>
+  </si>
+  <si>
+    <t>Marvin Cogle</t>
+  </si>
+  <si>
+    <t>Michael Colvin</t>
+  </si>
+  <si>
+    <t>Mike Basham</t>
+  </si>
+  <si>
+    <t>Mike Jones</t>
+  </si>
+  <si>
+    <t>Tyler Schliefert</t>
   </si>
 </sst>
 </file>
@@ -1059,106 +1116,593 @@
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H23" s="2"/>
-      <c r="I23" s="1"/>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>5570</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>46146.835416666669</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H24" s="2"/>
-      <c r="I24" s="1"/>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>5569</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="2">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="I24" s="1">
+        <v>46146.835416666669</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H25" s="2"/>
-      <c r="I25" s="1"/>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <v>5567</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>46146.836111111108</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H26" s="2"/>
-      <c r="I26" s="1"/>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>5553</v>
+      </c>
+      <c r="D26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>46146.836805555555</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H27" s="2"/>
       <c r="I27" s="1"/>
+      <c r="K27" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H28" s="2"/>
-      <c r="I28" s="1"/>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>5571</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="2">
+        <v>4.3287037037037035E-3</v>
+      </c>
+      <c r="I28" s="1">
+        <v>46146.837500000001</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H29" s="2"/>
-      <c r="I29" s="1"/>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29">
+        <v>5555</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="2">
+        <v>5.7986111111111112E-3</v>
+      </c>
+      <c r="I29" s="1">
+        <v>46146.837500000001</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H30" s="2"/>
-      <c r="I30" s="1"/>
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30">
+        <v>5556</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="2">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I30" s="1">
+        <v>46146.838194444441</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H31" s="2"/>
       <c r="I31" s="1"/>
+      <c r="K31" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H32" s="2"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H33" s="2"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32">
+        <v>5557</v>
+      </c>
+      <c r="D32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>46146.838888888888</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33">
+        <v>5554</v>
+      </c>
+      <c r="D33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>46146.838888888888</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H35" s="2"/>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35">
+        <v>5558</v>
+      </c>
+      <c r="D35" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="2">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I35" s="1">
+        <v>46146.839583333334</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H40" s="2"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H41" s="2"/>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H42" s="2"/>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H43" s="2"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H44" s="2"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H45" s="2"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37">
+        <v>5559</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>46146.840277777781</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38">
+        <v>5560</v>
+      </c>
+      <c r="D38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="2">
+        <v>5.1273148148148146E-3</v>
+      </c>
+      <c r="I38" s="1">
+        <v>46146.84097222222</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39">
+        <v>5561</v>
+      </c>
+      <c r="D39" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>46146.84097222222</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40">
+        <v>5562</v>
+      </c>
+      <c r="D40" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>46146.841666666667</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41">
+        <v>5563</v>
+      </c>
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>46146.842361111114</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42">
+        <v>5568</v>
+      </c>
+      <c r="D42" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="2">
+        <v>4.8726851851851848E-3</v>
+      </c>
+      <c r="I42" s="1">
+        <v>46146.842361111114</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43">
+        <v>5564</v>
+      </c>
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>46146.843055555553</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44">
+        <v>5566</v>
+      </c>
+      <c r="D44" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="2">
+        <v>4.8379629629629632E-3</v>
+      </c>
+      <c r="I44" s="1">
+        <v>46146.84375</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45">
+        <v>5565</v>
+      </c>
+      <c r="D45" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="2">
+        <v>6.0879629629629626E-3</v>
+      </c>
+      <c r="I45" s="1">
+        <v>46146.844444444447</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H46" s="2"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H47" s="2"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H48" s="2"/>
       <c r="I48" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608511CA-AFDC-44CE-BFBA-7B2BD587729E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3A096E-2E8F-4A9E-8912-27CFC13ADA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="44">
   <si>
     <t>Company Name</t>
   </si>
@@ -125,9 +125,6 @@
     <t>Bailey Bulyar</t>
   </si>
   <si>
-    <t>Bruce Willard</t>
-  </si>
-  <si>
     <t>Cory Volland</t>
   </si>
   <si>
@@ -158,22 +155,22 @@
     <t>Manny Rodenberg</t>
   </si>
   <si>
-    <t>Marcus Trimble</t>
-  </si>
-  <si>
     <t>Marvin Cogle</t>
   </si>
   <si>
     <t>Michael Colvin</t>
   </si>
   <si>
-    <t>Mike Basham</t>
-  </si>
-  <si>
     <t>Mike Jones</t>
   </si>
   <si>
     <t>Tyler Schliefert</t>
+  </si>
+  <si>
+    <t>Chase Bennett</t>
+  </si>
+  <si>
+    <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1175,7 @@
         <v>20</v>
       </c>
       <c r="C25">
-        <v>5567</v>
+        <v>5553</v>
       </c>
       <c r="D25" t="s">
         <v>28</v>
@@ -1187,13 +1184,13 @@
         <v>25</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
       </c>
       <c r="I25" s="1">
-        <v>46146.836111111108</v>
+        <v>46146.836805555555</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1203,39 +1200,39 @@
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+      <c r="H26" s="2"/>
+      <c r="I26" s="1"/>
+      <c r="K26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>20</v>
       </c>
-      <c r="C26">
-        <v>5553</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C27">
+        <v>5571</v>
+      </c>
+      <c r="D27" t="s">
         <v>29</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F27" t="s">
         <v>25</v>
       </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="2">
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4.3287037037037035E-3</v>
+      </c>
+      <c r="I27" s="1">
+        <v>46146.837500000001</v>
+      </c>
+      <c r="J27">
         <v>0</v>
       </c>
-      <c r="I26" s="1">
-        <v>46146.836805555555</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" t="s">
+      <c r="K27" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H27" s="2"/>
-      <c r="I27" s="1"/>
-      <c r="K27" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
@@ -1243,7 +1240,7 @@
         <v>20</v>
       </c>
       <c r="C28">
-        <v>5571</v>
+        <v>5555</v>
       </c>
       <c r="D28" t="s">
         <v>30</v>
@@ -1255,7 +1252,7 @@
         <v>10</v>
       </c>
       <c r="H28" s="2">
-        <v>4.3287037037037035E-3</v>
+        <v>5.7986111111111112E-3</v>
       </c>
       <c r="I28" s="1">
         <v>46146.837500000001</v>
@@ -1272,7 +1269,7 @@
         <v>20</v>
       </c>
       <c r="C29">
-        <v>5555</v>
+        <v>5556</v>
       </c>
       <c r="D29" t="s">
         <v>31</v>
@@ -1281,13 +1278,13 @@
         <v>25</v>
       </c>
       <c r="G29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H29" s="2">
-        <v>5.7986111111111112E-3</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="I29" s="1">
-        <v>46146.837500000001</v>
+        <v>46146.838194444441</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1297,39 +1294,39 @@
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+      <c r="H30" s="2"/>
+      <c r="I30" s="1"/>
+      <c r="K30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
         <v>20</v>
       </c>
-      <c r="C30">
-        <v>5556</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C31">
+        <v>5557</v>
+      </c>
+      <c r="D31" t="s">
         <v>32</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F31" t="s">
         <v>25</v>
       </c>
-      <c r="G30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" s="2">
-        <v>2.199074074074074E-4</v>
-      </c>
-      <c r="I30" s="1">
-        <v>46146.838194444441</v>
-      </c>
-      <c r="J30">
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="2">
         <v>0</v>
       </c>
-      <c r="K30" t="s">
+      <c r="I31" s="1">
+        <v>46146.838888888888</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H31" s="2"/>
-      <c r="I31" s="1"/>
-      <c r="K31" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
@@ -1337,7 +1334,7 @@
         <v>20</v>
       </c>
       <c r="C32">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="D32" t="s">
         <v>33</v>
@@ -1346,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -1362,75 +1359,75 @@
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
+      <c r="H33" s="2"/>
+      <c r="I33" s="1"/>
+      <c r="K33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>20</v>
       </c>
-      <c r="C33">
-        <v>5554</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C34">
+        <v>5558</v>
+      </c>
+      <c r="D34" t="s">
         <v>34</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>25</v>
       </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="2">
+      <c r="G34" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="2">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I34" s="1">
+        <v>46146.839583333334</v>
+      </c>
+      <c r="J34">
         <v>0</v>
       </c>
-      <c r="I33" s="1">
-        <v>46146.838888888888</v>
-      </c>
-      <c r="J33">
+      <c r="K34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H35" s="2"/>
+      <c r="I35" s="1"/>
+      <c r="K35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36">
+        <v>5559</v>
+      </c>
+      <c r="D36" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="2">
         <v>0</v>
       </c>
-      <c r="K33" t="s">
+      <c r="I36" s="1">
+        <v>46146.840277777781</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H34" s="2"/>
-      <c r="I34" s="1"/>
-      <c r="K34" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35">
-        <v>5558</v>
-      </c>
-      <c r="D35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F35" t="s">
-        <v>25</v>
-      </c>
-      <c r="G35" t="s">
-        <v>12</v>
-      </c>
-      <c r="H35" s="2">
-        <v>4.3981481481481481E-4</v>
-      </c>
-      <c r="I35" s="1">
-        <v>46146.839583333334</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H36" s="2"/>
-      <c r="I36" s="1"/>
-      <c r="K36" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
@@ -1438,7 +1435,7 @@
         <v>20</v>
       </c>
       <c r="C37">
-        <v>5559</v>
+        <v>5560</v>
       </c>
       <c r="D37" t="s">
         <v>36</v>
@@ -1447,13 +1444,13 @@
         <v>25</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H37" s="2">
-        <v>0</v>
+        <v>5.1273148148148146E-3</v>
       </c>
       <c r="I37" s="1">
-        <v>46146.840277777781</v>
+        <v>46146.84097222222</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1467,7 +1464,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>5560</v>
+        <v>5561</v>
       </c>
       <c r="D38" t="s">
         <v>37</v>
@@ -1476,10 +1473,10 @@
         <v>25</v>
       </c>
       <c r="G38" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H38" s="2">
-        <v>5.1273148148148146E-3</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1">
         <v>46146.84097222222</v>
@@ -1496,7 +1493,7 @@
         <v>20</v>
       </c>
       <c r="C39">
-        <v>5561</v>
+        <v>5563</v>
       </c>
       <c r="D39" t="s">
         <v>38</v>
@@ -1511,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="1">
-        <v>46146.84097222222</v>
+        <v>46146.842361111114</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -1525,7 +1522,7 @@
         <v>20</v>
       </c>
       <c r="C40">
-        <v>5562</v>
+        <v>5568</v>
       </c>
       <c r="D40" t="s">
         <v>39</v>
@@ -1534,13 +1531,13 @@
         <v>25</v>
       </c>
       <c r="G40" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H40" s="2">
-        <v>0</v>
+        <v>4.8726851851851848E-3</v>
       </c>
       <c r="I40" s="1">
-        <v>46146.841666666667</v>
+        <v>46146.842361111114</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -1554,7 +1551,7 @@
         <v>20</v>
       </c>
       <c r="C41">
-        <v>5563</v>
+        <v>5566</v>
       </c>
       <c r="D41" t="s">
         <v>40</v>
@@ -1563,13 +1560,13 @@
         <v>25</v>
       </c>
       <c r="G41" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H41" s="2">
-        <v>0</v>
+        <v>4.8379629629629632E-3</v>
       </c>
       <c r="I41" s="1">
-        <v>46146.842361111114</v>
+        <v>46146.84375</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -1583,7 +1580,7 @@
         <v>20</v>
       </c>
       <c r="C42">
-        <v>5568</v>
+        <v>5565</v>
       </c>
       <c r="D42" t="s">
         <v>41</v>
@@ -1595,10 +1592,10 @@
         <v>10</v>
       </c>
       <c r="H42" s="2">
-        <v>4.8726851851851848E-3</v>
+        <v>6.0879629629629626E-3</v>
       </c>
       <c r="I42" s="1">
-        <v>46146.842361111114</v>
+        <v>46146.844444444447</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -1612,7 +1609,7 @@
         <v>20</v>
       </c>
       <c r="C43">
-        <v>5564</v>
+        <v>5662</v>
       </c>
       <c r="D43" t="s">
         <v>42</v>
@@ -1621,13 +1618,13 @@
         <v>25</v>
       </c>
       <c r="G43" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H43" s="2">
-        <v>0</v>
+        <v>4.2592592592592595E-3</v>
       </c>
       <c r="I43" s="1">
-        <v>46146.843055555553</v>
+        <v>46163.668749999997</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -1641,22 +1638,22 @@
         <v>20</v>
       </c>
       <c r="C44">
-        <v>5566</v>
+        <v>5556</v>
       </c>
       <c r="D44" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" t="s">
         <v>43</v>
       </c>
-      <c r="F44" t="s">
-        <v>25</v>
-      </c>
       <c r="G44" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H44" s="2">
-        <v>4.8379629629629632E-3</v>
+        <v>2.5462962962962961E-4</v>
       </c>
       <c r="I44" s="1">
-        <v>46146.84375</v>
+        <v>46163.918749999997</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -1666,32 +1663,10 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45">
-        <v>5565</v>
-      </c>
-      <c r="D45" t="s">
-        <v>44</v>
-      </c>
-      <c r="F45" t="s">
-        <v>25</v>
-      </c>
-      <c r="G45" t="s">
-        <v>10</v>
-      </c>
-      <c r="H45" s="2">
-        <v>6.0879629629629626E-3</v>
-      </c>
-      <c r="I45" s="1">
-        <v>46146.844444444447</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="1"/>
       <c r="K45" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Brads Towing- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Brads-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589E4F6D-D55C-487A-A06A-661FBFF3F800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FFF0E7-0283-4EA8-87B8-C02320788D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2164,7 +2164,7 @@
         <v>46175.802777777775</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Brads-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55D3D038-60ED-4186-863A-68094F439A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F5E1A45-7CBA-4A7F-8AF1-A9C34BB9AF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="52">
   <si>
     <t>Company Name</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Rules for Safe Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
@@ -189,6 +192,9 @@
   </si>
   <si>
     <t>Kenny Purdue</t>
+  </si>
+  <si>
+    <t>Josh Dobney</t>
   </si>
 </sst>
 </file>
@@ -562,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -611,13 +617,13 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>4962</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>16</v>
@@ -640,13 +646,13 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>4964</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>16</v>
@@ -673,18 +679,18 @@
       <c r="J4" s="2"/>
       <c r="K4" s="1"/>
       <c r="M4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>4965</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
@@ -707,13 +713,13 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>4963</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
@@ -736,16 +742,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>4962</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -765,16 +771,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>4964</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>14</v>
@@ -798,21 +804,21 @@
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
       <c r="M9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10">
         <v>4965</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -832,16 +838,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11">
         <v>4963</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -861,16 +867,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12">
         <v>4962</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -890,16 +896,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13">
         <v>4965</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -919,16 +925,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14">
         <v>4963</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>14</v>
@@ -952,21 +958,21 @@
       <c r="J15" s="2"/>
       <c r="K15" s="1"/>
       <c r="M15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16">
         <v>4962</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>12</v>
@@ -990,21 +996,21 @@
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
       <c r="M17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E18">
         <v>4965</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -1024,16 +1030,16 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E19">
         <v>4963</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -1053,13 +1059,13 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20">
         <v>4962</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>17</v>
@@ -1082,13 +1088,13 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21">
         <v>4965</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>17</v>
@@ -1111,13 +1117,13 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E22">
         <v>4963</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>17</v>
@@ -1140,13 +1146,13 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E23">
         <v>5570</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>17</v>
@@ -1169,13 +1175,13 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E24">
         <v>5569</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>17</v>
@@ -1198,13 +1204,13 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E25">
         <v>5553</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>17</v>
@@ -1231,18 +1237,18 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E27">
         <v>5571</v>
       </c>
       <c r="F27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>17</v>
@@ -1265,13 +1271,13 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E28">
         <v>5555</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>17</v>
@@ -1294,13 +1300,13 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E29">
         <v>5556</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>17</v>
@@ -1327,18 +1333,18 @@
       <c r="J30" s="2"/>
       <c r="K30" s="1"/>
       <c r="M30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E31">
         <v>5557</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>17</v>
@@ -1361,13 +1367,13 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E32">
         <v>5554</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>17</v>
@@ -1394,18 +1400,18 @@
       <c r="J33" s="2"/>
       <c r="K33" s="1"/>
       <c r="M33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E34">
         <v>5558</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>17</v>
@@ -1432,18 +1438,18 @@
       <c r="J35" s="2"/>
       <c r="K35" s="1"/>
       <c r="M35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E36">
         <v>5559</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>17</v>
@@ -1466,13 +1472,13 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E37">
         <v>5560</v>
       </c>
       <c r="F37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>17</v>
@@ -1495,13 +1501,13 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E38">
         <v>5561</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>17</v>
@@ -1524,13 +1530,13 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E39">
         <v>5563</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>17</v>
@@ -1553,13 +1559,13 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E40">
         <v>5568</v>
       </c>
       <c r="F40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>17</v>
@@ -1582,13 +1588,13 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E41">
         <v>5566</v>
       </c>
       <c r="F41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>17</v>
@@ -1611,13 +1617,13 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E42">
         <v>5565</v>
       </c>
       <c r="F42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>17</v>
@@ -1640,13 +1646,13 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E43">
         <v>5662</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>17</v>
@@ -1669,16 +1675,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E44">
         <v>5556</v>
       </c>
       <c r="F44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>12</v>
@@ -1690,7 +1696,7 @@
         <v>46163.918749999997</v>
       </c>
       <c r="L44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" t="s">
         <v>11</v>
@@ -1702,21 +1708,21 @@
       <c r="J45" s="2"/>
       <c r="K45" s="1"/>
       <c r="M45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E46">
         <v>5749</v>
       </c>
       <c r="F46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -1728,7 +1734,7 @@
         <v>46170.377662037034</v>
       </c>
       <c r="L46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M46" t="s">
         <v>11</v>
@@ -1736,16 +1742,16 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E47">
         <v>5748</v>
       </c>
       <c r="F47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>13</v>
@@ -1757,7 +1763,7 @@
         <v>46170.377662037034</v>
       </c>
       <c r="L47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M47" t="s">
         <v>11</v>
@@ -1765,13 +1771,13 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E48">
         <v>5749</v>
       </c>
       <c r="F48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -1794,13 +1800,13 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E49">
         <v>5560</v>
       </c>
       <c r="F49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -1823,13 +1829,13 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E50">
         <v>5565</v>
       </c>
       <c r="F50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -1852,16 +1858,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E51">
         <v>4962</v>
       </c>
       <c r="F51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -1881,16 +1887,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E52">
         <v>5569</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>12</v>
@@ -1914,21 +1920,21 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
       <c r="M53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E54">
         <v>5553</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -1948,16 +1954,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E55">
         <v>5571</v>
       </c>
       <c r="F55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>13</v>
@@ -1977,16 +1983,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E56">
         <v>5555</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2006,16 +2012,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E57">
         <v>5748</v>
       </c>
       <c r="F57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>13</v>
@@ -2035,16 +2041,16 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E58">
         <v>5556</v>
       </c>
       <c r="F58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>13</v>
@@ -2064,16 +2070,16 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E59">
         <v>5557</v>
       </c>
       <c r="F59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2093,16 +2099,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E60">
         <v>5554</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2122,16 +2128,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E61">
         <v>4963</v>
       </c>
       <c r="F61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2151,16 +2157,16 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E62">
         <v>5558</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2180,16 +2186,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E63">
         <v>5559</v>
       </c>
       <c r="F63" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>13</v>
@@ -2209,16 +2215,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E64">
         <v>5561</v>
       </c>
       <c r="F64" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2238,16 +2244,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E65">
         <v>5563</v>
       </c>
       <c r="F65" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>13</v>
@@ -2267,16 +2273,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E66">
         <v>5568</v>
       </c>
       <c r="F66" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2296,22 +2302,22 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E67">
         <v>5566</v>
       </c>
       <c r="F67" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J67" s="2">
-        <v>0</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K67" s="1">
         <v>46175.805555555555</v>
@@ -2325,16 +2331,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E68">
         <v>5558</v>
       </c>
       <c r="F68" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>14</v>
@@ -2346,7 +2352,7 @@
         <v>46203.711111111108</v>
       </c>
       <c r="L68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" t="s">
         <v>11</v>
@@ -2358,21 +2364,21 @@
       <c r="J69" s="2"/>
       <c r="K69" s="1"/>
       <c r="M69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E70">
         <v>5944</v>
       </c>
       <c r="F70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>12</v>
@@ -2396,154 +2402,640 @@
       <c r="J71" s="2"/>
       <c r="K71" s="1"/>
       <c r="M71" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H72" s="2"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="1"/>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72">
+        <v>4962</v>
+      </c>
+      <c r="F72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J72" s="2">
+        <v>5.5092592592592589E-3</v>
+      </c>
+      <c r="K72" s="1">
+        <v>46210.669791666667</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H73" s="2"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="1"/>
+      <c r="D73" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73">
+        <v>5569</v>
+      </c>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J73" s="2">
+        <v>5.3935185185185188E-3</v>
+      </c>
+      <c r="K73" s="1">
+        <v>46210.670486111114</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H74" s="2"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="1"/>
+      <c r="D74" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74">
+        <v>5749</v>
+      </c>
+      <c r="F74" t="s">
+        <v>48</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1">
+        <v>46210.671180555553</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H75" s="2"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="1"/>
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75">
+        <v>5553</v>
+      </c>
+      <c r="F75" t="s">
+        <v>34</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J75" s="2">
+        <v>6.122685185185185E-3</v>
+      </c>
+      <c r="K75" s="1">
+        <v>46210.671875</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H76" s="2"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="1"/>
+      <c r="D76" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76">
+        <v>5571</v>
+      </c>
+      <c r="F76" t="s">
+        <v>35</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J76" s="2">
+        <v>1.3009259259259259E-2</v>
+      </c>
+      <c r="K76" s="1">
+        <v>46210.671875</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H77" s="2"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="1"/>
+      <c r="D77" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77">
+        <v>5555</v>
+      </c>
+      <c r="F77" t="s">
+        <v>36</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J77" s="2">
+        <v>6.3078703703703708E-3</v>
+      </c>
+      <c r="K77" s="1">
+        <v>46210.672569444447</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H78" s="2"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="1"/>
+      <c r="D78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78">
+        <v>5748</v>
+      </c>
+      <c r="F78" t="s">
+        <v>49</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1">
+        <v>46210.673263888886</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H79" s="2"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="1"/>
+      <c r="D79" t="s">
+        <v>28</v>
+      </c>
+      <c r="E79">
+        <v>5556</v>
+      </c>
+      <c r="F79" t="s">
+        <v>37</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>46210.673958333333</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H80" s="2"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="1"/>
-    </row>
-    <row r="81" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H81" s="2"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="1"/>
-    </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H82" s="2"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="1"/>
-    </row>
-    <row r="83" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H83" s="2"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="1"/>
-    </row>
-    <row r="84" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H84" s="2"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="1"/>
-    </row>
-    <row r="85" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H85" s="2"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="1"/>
-    </row>
-    <row r="86" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H86" s="2"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="1"/>
-    </row>
-    <row r="87" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H87" s="2"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="1"/>
-    </row>
-    <row r="88" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D80" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80">
+        <v>5557</v>
+      </c>
+      <c r="F80" t="s">
+        <v>38</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J80" s="2">
+        <v>2.3333333333333334E-2</v>
+      </c>
+      <c r="K80" s="1">
+        <v>46210.67465277778</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D81" t="s">
+        <v>28</v>
+      </c>
+      <c r="E81">
+        <v>5554</v>
+      </c>
+      <c r="F81" t="s">
+        <v>39</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J81" s="2">
+        <v>7.0717592592592594E-3</v>
+      </c>
+      <c r="K81" s="1">
+        <v>46210.67465277778</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D82" t="s">
+        <v>28</v>
+      </c>
+      <c r="E82">
+        <v>4963</v>
+      </c>
+      <c r="F82" t="s">
+        <v>32</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J82" s="2">
+        <v>6.1689814814814819E-3</v>
+      </c>
+      <c r="K82" s="1">
+        <v>46210.675347222219</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D83" t="s">
+        <v>28</v>
+      </c>
+      <c r="E83">
+        <v>5558</v>
+      </c>
+      <c r="F83" t="s">
+        <v>40</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J83" s="2">
+        <v>8.2060185185185187E-3</v>
+      </c>
+      <c r="K83" s="1">
+        <v>46210.676041666666</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D84" t="s">
+        <v>28</v>
+      </c>
+      <c r="E84">
+        <v>5559</v>
+      </c>
+      <c r="F84" t="s">
+        <v>41</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J84" s="2">
+        <v>7.1064814814814819E-3</v>
+      </c>
+      <c r="K84" s="1">
+        <v>46210.676736111112</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D85" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85">
+        <v>5932</v>
+      </c>
+      <c r="F85" t="s">
+        <v>51</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J85" s="2">
+        <v>6.9675925925925929E-3</v>
+      </c>
+      <c r="K85" s="1">
+        <v>46210.677430555559</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D86" t="s">
+        <v>28</v>
+      </c>
+      <c r="E86">
+        <v>5560</v>
+      </c>
+      <c r="F86" t="s">
+        <v>42</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J86" s="2">
+        <v>7.7546296296296295E-3</v>
+      </c>
+      <c r="K86" s="1">
+        <v>46210.677430555559</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D87" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87">
+        <v>5944</v>
+      </c>
+      <c r="F87" t="s">
+        <v>50</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J87" s="2">
+        <v>1.8668981481481481E-2</v>
+      </c>
+      <c r="K87" s="1">
+        <v>46210.678124999999</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H88" s="2"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
       <c r="K88" s="1"/>
-    </row>
-    <row r="89" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H89" s="2"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="1"/>
-    </row>
-    <row r="90" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H90" s="2"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="1"/>
-    </row>
-    <row r="91" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H91" s="2"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="1"/>
-    </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H92" s="2"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="1"/>
-    </row>
-    <row r="93" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H93" s="2"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="1"/>
-    </row>
-    <row r="94" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M88" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D89" t="s">
+        <v>28</v>
+      </c>
+      <c r="E89">
+        <v>5561</v>
+      </c>
+      <c r="F89" t="s">
+        <v>43</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J89" s="2">
+        <v>8.6574074074074071E-3</v>
+      </c>
+      <c r="K89" s="1">
+        <v>46210.678819444445</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D90" t="s">
+        <v>28</v>
+      </c>
+      <c r="E90">
+        <v>5563</v>
+      </c>
+      <c r="F90" t="s">
+        <v>44</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J90" s="2">
+        <v>5.9722222222222225E-3</v>
+      </c>
+      <c r="K90" s="1">
+        <v>46210.680208333331</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D91" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91">
+        <v>5568</v>
+      </c>
+      <c r="F91" t="s">
+        <v>45</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J91" s="2">
+        <v>6.3888888888888893E-3</v>
+      </c>
+      <c r="K91" s="1">
+        <v>46210.680902777778</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D92" t="s">
+        <v>28</v>
+      </c>
+      <c r="E92">
+        <v>5566</v>
+      </c>
+      <c r="F92" t="s">
+        <v>46</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J92" s="2">
+        <v>5.9837962962962961E-3</v>
+      </c>
+      <c r="K92" s="1">
+        <v>46210.680902777778</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D93" t="s">
+        <v>28</v>
+      </c>
+      <c r="E93">
+        <v>5565</v>
+      </c>
+      <c r="F93" t="s">
+        <v>47</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J93" s="2">
+        <v>6.7824074074074071E-3</v>
+      </c>
+      <c r="K93" s="1">
+        <v>46210.681597222225</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H94" s="2"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
       <c r="K94" s="1"/>
     </row>
-    <row r="95" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H95" s="2"/>
       <c r="I95" s="1"/>
       <c r="J95" s="2"/>
       <c r="K95" s="1"/>
     </row>
-    <row r="96" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H96" s="2"/>
       <c r="I96" s="1"/>
       <c r="J96" s="2"/>
@@ -4238,6 +4730,7 @@
     <row r="378" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H378" s="2"/>
       <c r="I378" s="1"/>
+      <c r="J378" s="2"/>
       <c r="K378" s="1"/>
     </row>
     <row r="379" spans="8:11" x14ac:dyDescent="0.3">
@@ -40304,7 +40797,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Brads-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F5E1A45-7CBA-4A7F-8AF1-A9C34BB9AF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1197BD01-D8D2-4C69-9602-6A4D18657BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="52">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,7 +86,7 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
   </si>
   <si>
     <t>December Driving Edition</t>
@@ -98,19 +98,19 @@
     <t>Driver Health</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
-    <t>Speed Mangement-C</t>
+    <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
-    <t>Safe Lifting for Commercial Drivers</t>
+    <t>Drowsy Driving</t>
+  </si>
+  <si>
+    <t>Speed Mangement-C</t>
   </si>
   <si>
     <t>Austin Simms</t>
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -679,7 +679,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="1"/>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
@@ -751,7 +751,7 @@
         <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -780,7 +780,7 @@
         <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>14</v>
@@ -804,7 +804,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
       <c r="M9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
@@ -818,7 +818,7 @@
         <v>31</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -847,7 +847,7 @@
         <v>32</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -876,7 +876,7 @@
         <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -905,7 +905,7 @@
         <v>31</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -934,7 +934,7 @@
         <v>32</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>14</v>
@@ -958,7 +958,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="1"/>
       <c r="M15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
@@ -972,7 +972,7 @@
         <v>29</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>12</v>
@@ -996,7 +996,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
       <c r="M17" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
@@ -1010,7 +1010,7 @@
         <v>31</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -1039,7 +1039,7 @@
         <v>32</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -1237,7 +1237,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1333,7 +1333,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="1"/>
       <c r="M30" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
@@ -1400,7 +1400,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="1"/>
       <c r="M33" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
@@ -1438,7 +1438,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="1"/>
       <c r="M35" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
@@ -1687,10 +1687,10 @@
         <v>26</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J44" s="2">
-        <v>2.5462962962962961E-4</v>
+        <v>0.2714699074074074</v>
       </c>
       <c r="K44" s="1">
         <v>46163.918749999997</v>
@@ -1703,12 +1703,32 @@
       </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H45" s="2"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="1"/>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45">
+        <v>5749</v>
+      </c>
+      <c r="F45" t="s">
+        <v>48</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>46170.377662037034</v>
+      </c>
+      <c r="L45">
+        <v>3</v>
+      </c>
       <c r="M45" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
@@ -1716,10 +1736,10 @@
         <v>28</v>
       </c>
       <c r="E46">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="F46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>26</v>
@@ -1745,25 +1765,25 @@
         <v>28</v>
       </c>
       <c r="E47">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="F47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J47" s="2">
+        <v>3.802083333333333E-2</v>
+      </c>
+      <c r="K47" s="1">
+        <v>46174.516550925924</v>
+      </c>
+      <c r="L47">
         <v>0</v>
-      </c>
-      <c r="K47" s="1">
-        <v>46170.377662037034</v>
-      </c>
-      <c r="L47">
-        <v>3</v>
       </c>
       <c r="M47" t="s">
         <v>11</v>
@@ -1774,22 +1794,22 @@
         <v>28</v>
       </c>
       <c r="E48">
-        <v>5749</v>
+        <v>5560</v>
       </c>
       <c r="F48" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J48" s="2">
-        <v>3.802083333333333E-2</v>
+        <v>1.6585648148148148E-2</v>
       </c>
       <c r="K48" s="1">
-        <v>46174.516550925924</v>
+        <v>46174.545138888891</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -1803,22 +1823,22 @@
         <v>28</v>
       </c>
       <c r="E49">
-        <v>5560</v>
+        <v>5565</v>
       </c>
       <c r="F49" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J49" s="2">
-        <v>1.6585648148148148E-2</v>
+        <v>8.3912037037037045E-3</v>
       </c>
       <c r="K49" s="1">
-        <v>46174.545138888891</v>
+        <v>46174.547222222223</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -1832,25 +1852,25 @@
         <v>28</v>
       </c>
       <c r="E50">
-        <v>5565</v>
+        <v>4962</v>
       </c>
       <c r="F50" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J50" s="2">
-        <v>8.3912037037037045E-3</v>
+        <v>9.0740740740740747E-3</v>
       </c>
       <c r="K50" s="1">
-        <v>46174.547222222223</v>
+        <v>46175.795138888891</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="s">
         <v>11</v>
@@ -1861,22 +1881,22 @@
         <v>28</v>
       </c>
       <c r="E51">
-        <v>4962</v>
+        <v>5569</v>
       </c>
       <c r="F51" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J51" s="2">
-        <v>9.0740740740740747E-3</v>
+        <v>4.2824074074074075E-4</v>
       </c>
       <c r="K51" s="1">
-        <v>46175.795138888891</v>
+        <v>46175.796527777777</v>
       </c>
       <c r="L51">
         <v>1</v>
@@ -1886,41 +1906,41 @@
       </c>
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D52" t="s">
+      <c r="H52" s="2"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="1"/>
+      <c r="M52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
         <v>28</v>
       </c>
-      <c r="E52">
-        <v>5569</v>
-      </c>
-      <c r="F52" t="s">
-        <v>33</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J52" s="2">
-        <v>4.2824074074074075E-4</v>
-      </c>
-      <c r="K52" s="1">
-        <v>46175.796527777777</v>
-      </c>
-      <c r="L52">
-        <v>1</v>
-      </c>
-      <c r="M52" t="s">
+      <c r="E53">
+        <v>5553</v>
+      </c>
+      <c r="F53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J53" s="2">
+        <v>7.5231481481481477E-3</v>
+      </c>
+      <c r="K53" s="1">
+        <v>46175.79791666667</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H53" s="2"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="1"/>
-      <c r="M53" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
@@ -1928,25 +1948,25 @@
         <v>28</v>
       </c>
       <c r="E54">
-        <v>5553</v>
+        <v>5571</v>
       </c>
       <c r="F54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J54" s="2">
-        <v>7.5231481481481477E-3</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>46175.79791666667</v>
+        <v>46175.798611111109</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="s">
         <v>11</v>
@@ -1957,25 +1977,25 @@
         <v>28</v>
       </c>
       <c r="E55">
-        <v>5571</v>
+        <v>5555</v>
       </c>
       <c r="F55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J55" s="2">
+        <v>7.5347222222222222E-3</v>
+      </c>
+      <c r="K55" s="1">
+        <v>46175.799305555556</v>
+      </c>
+      <c r="L55">
         <v>0</v>
-      </c>
-      <c r="K55" s="1">
-        <v>46175.798611111109</v>
-      </c>
-      <c r="L55">
-        <v>1</v>
       </c>
       <c r="M55" t="s">
         <v>11</v>
@@ -1986,25 +2006,25 @@
         <v>28</v>
       </c>
       <c r="E56">
-        <v>5555</v>
+        <v>5748</v>
       </c>
       <c r="F56" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J56" s="2">
-        <v>7.5347222222222222E-3</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>46175.799305555556</v>
+        <v>46175.8</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="s">
         <v>11</v>
@@ -2015,13 +2035,13 @@
         <v>28</v>
       </c>
       <c r="E57">
-        <v>5748</v>
+        <v>5556</v>
       </c>
       <c r="F57" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>13</v>
@@ -2030,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>46175.8</v>
+        <v>46175.800694444442</v>
       </c>
       <c r="L57">
         <v>1</v>
@@ -2044,13 +2064,13 @@
         <v>28</v>
       </c>
       <c r="E58">
-        <v>5556</v>
+        <v>5557</v>
       </c>
       <c r="F58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>13</v>
@@ -2059,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>46175.800694444442</v>
+        <v>46175.801388888889</v>
       </c>
       <c r="L58">
         <v>1</v>
@@ -2073,13 +2093,13 @@
         <v>28</v>
       </c>
       <c r="E59">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="F59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2088,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="1">
-        <v>46175.801388888889</v>
+        <v>46175.802083333336</v>
       </c>
       <c r="L59">
         <v>1</v>
@@ -2102,13 +2122,13 @@
         <v>28</v>
       </c>
       <c r="E60">
-        <v>5554</v>
+        <v>4963</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2131,25 +2151,25 @@
         <v>28</v>
       </c>
       <c r="E61">
-        <v>4963</v>
+        <v>5558</v>
       </c>
       <c r="F61" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J61" s="2">
-        <v>0</v>
+        <v>1.1631944444444445E-2</v>
       </c>
       <c r="K61" s="1">
-        <v>46175.802083333336</v>
+        <v>46175.802777777775</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M61" t="s">
         <v>11</v>
@@ -2160,25 +2180,25 @@
         <v>28</v>
       </c>
       <c r="E62">
-        <v>5558</v>
+        <v>5559</v>
       </c>
       <c r="F62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J62" s="2">
-        <v>1.1631944444444445E-2</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>46175.802777777775</v>
+        <v>46175.803472222222</v>
       </c>
       <c r="L62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" t="s">
         <v>11</v>
@@ -2189,22 +2209,22 @@
         <v>28</v>
       </c>
       <c r="E63">
-        <v>5559</v>
+        <v>5561</v>
       </c>
       <c r="F63" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J63" s="2">
-        <v>0</v>
+        <v>9.5370370370370366E-3</v>
       </c>
       <c r="K63" s="1">
-        <v>46175.803472222222</v>
+        <v>46175.804166666669</v>
       </c>
       <c r="L63">
         <v>1</v>
@@ -2218,22 +2238,22 @@
         <v>28</v>
       </c>
       <c r="E64">
-        <v>5561</v>
+        <v>5563</v>
       </c>
       <c r="F64" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J64" s="2">
-        <v>9.5370370370370366E-3</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>46175.804166666669</v>
+        <v>46175.804861111108</v>
       </c>
       <c r="L64">
         <v>1</v>
@@ -2247,13 +2267,13 @@
         <v>28</v>
       </c>
       <c r="E65">
-        <v>5563</v>
+        <v>5568</v>
       </c>
       <c r="F65" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>13</v>
@@ -2276,22 +2296,22 @@
         <v>28</v>
       </c>
       <c r="E66">
-        <v>5568</v>
+        <v>5566</v>
       </c>
       <c r="F66" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J66" s="2">
-        <v>0</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K66" s="1">
-        <v>46175.804861111108</v>
+        <v>46175.805555555555</v>
       </c>
       <c r="L66">
         <v>1</v>
@@ -2305,104 +2325,104 @@
         <v>28</v>
       </c>
       <c r="E67">
-        <v>5566</v>
+        <v>5558</v>
       </c>
       <c r="F67" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J67" s="2">
-        <v>6.9444444444444441E-3</v>
+        <v>1.8703703703703705E-2</v>
       </c>
       <c r="K67" s="1">
-        <v>46175.805555555555</v>
+        <v>46203.711111111108</v>
       </c>
       <c r="L67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D68" t="s">
+      <c r="H68" s="2"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="1"/>
+      <c r="M68" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D69" t="s">
         <v>28</v>
       </c>
-      <c r="E68">
-        <v>5558</v>
-      </c>
-      <c r="F68" t="s">
-        <v>40</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J68" s="2">
+      <c r="E69">
+        <v>5944</v>
+      </c>
+      <c r="F69" t="s">
+        <v>50</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J69" s="2">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="K69" s="1">
+        <v>46204.585648148146</v>
+      </c>
+      <c r="L69">
         <v>0</v>
       </c>
-      <c r="K68" s="1">
-        <v>46203.711111111108</v>
-      </c>
-      <c r="L68">
-        <v>2</v>
-      </c>
-      <c r="M68" t="s">
+      <c r="M69" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H69" s="2"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="1"/>
-      <c r="M69" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D70" t="s">
+      <c r="H70" s="2"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="1"/>
+      <c r="M70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D71" t="s">
         <v>28</v>
       </c>
-      <c r="E70">
-        <v>5944</v>
-      </c>
-      <c r="F70" t="s">
-        <v>50</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J70" s="2">
-        <v>1.5162037037037036E-3</v>
-      </c>
-      <c r="K70" s="1">
-        <v>46204.585648148146</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70" t="s">
+      <c r="E71">
+        <v>4962</v>
+      </c>
+      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J71" s="2">
+        <v>5.5092592592592589E-3</v>
+      </c>
+      <c r="K71" s="1">
+        <v>46210.669791666667</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H71" s="2"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="1"/>
-      <c r="M71" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
@@ -2410,10 +2430,10 @@
         <v>28</v>
       </c>
       <c r="E72">
-        <v>4962</v>
+        <v>5569</v>
       </c>
       <c r="F72" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>18</v>
@@ -2422,13 +2442,13 @@
         <v>10</v>
       </c>
       <c r="J72" s="2">
-        <v>5.5092592592592589E-3</v>
+        <v>5.3935185185185188E-3</v>
       </c>
       <c r="K72" s="1">
-        <v>46210.669791666667</v>
+        <v>46210.670486111114</v>
       </c>
       <c r="L72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="s">
         <v>11</v>
@@ -2439,25 +2459,25 @@
         <v>28</v>
       </c>
       <c r="E73">
-        <v>5569</v>
+        <v>5749</v>
       </c>
       <c r="F73" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J73" s="2">
-        <v>5.3935185185185188E-3</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>46210.670486111114</v>
+        <v>46210.671180555553</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="s">
         <v>11</v>
@@ -2468,25 +2488,25 @@
         <v>28</v>
       </c>
       <c r="E74">
-        <v>5749</v>
+        <v>5553</v>
       </c>
       <c r="F74" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J74" s="2">
+        <v>6.122685185185185E-3</v>
+      </c>
+      <c r="K74" s="1">
+        <v>46210.671875</v>
+      </c>
+      <c r="L74">
         <v>0</v>
-      </c>
-      <c r="K74" s="1">
-        <v>46210.671180555553</v>
-      </c>
-      <c r="L74">
-        <v>1</v>
       </c>
       <c r="M74" t="s">
         <v>11</v>
@@ -2497,10 +2517,10 @@
         <v>28</v>
       </c>
       <c r="E75">
-        <v>5553</v>
+        <v>5571</v>
       </c>
       <c r="F75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>18</v>
@@ -2509,7 +2529,7 @@
         <v>10</v>
       </c>
       <c r="J75" s="2">
-        <v>6.122685185185185E-3</v>
+        <v>1.3009259259259259E-2</v>
       </c>
       <c r="K75" s="1">
         <v>46210.671875</v>
@@ -2526,10 +2546,10 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>5571</v>
+        <v>5555</v>
       </c>
       <c r="F76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>18</v>
@@ -2538,10 +2558,10 @@
         <v>10</v>
       </c>
       <c r="J76" s="2">
-        <v>1.3009259259259259E-2</v>
+        <v>6.3078703703703708E-3</v>
       </c>
       <c r="K76" s="1">
-        <v>46210.671875</v>
+        <v>46210.672569444447</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -2555,25 +2575,25 @@
         <v>28</v>
       </c>
       <c r="E77">
-        <v>5555</v>
+        <v>5748</v>
       </c>
       <c r="F77" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J77" s="2">
-        <v>6.3078703703703708E-3</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>46210.672569444447</v>
+        <v>46210.673263888886</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="s">
         <v>11</v>
@@ -2584,22 +2604,22 @@
         <v>28</v>
       </c>
       <c r="E78">
-        <v>5748</v>
+        <v>5556</v>
       </c>
       <c r="F78" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J78" s="2">
-        <v>0</v>
+        <v>6.7476851851851856E-3</v>
       </c>
       <c r="K78" s="1">
-        <v>46210.673263888886</v>
+        <v>46210.673958333333</v>
       </c>
       <c r="L78">
         <v>1</v>
@@ -2613,25 +2633,25 @@
         <v>28</v>
       </c>
       <c r="E79">
-        <v>5556</v>
+        <v>5557</v>
       </c>
       <c r="F79" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J79" s="2">
+        <v>2.3333333333333334E-2</v>
+      </c>
+      <c r="K79" s="1">
+        <v>46210.67465277778</v>
+      </c>
+      <c r="L79">
         <v>0</v>
-      </c>
-      <c r="K79" s="1">
-        <v>46210.673958333333</v>
-      </c>
-      <c r="L79">
-        <v>1</v>
       </c>
       <c r="M79" t="s">
         <v>11</v>
@@ -2642,10 +2662,10 @@
         <v>28</v>
       </c>
       <c r="E80">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="F80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>18</v>
@@ -2654,7 +2674,7 @@
         <v>10</v>
       </c>
       <c r="J80" s="2">
-        <v>2.3333333333333334E-2</v>
+        <v>7.0717592592592594E-3</v>
       </c>
       <c r="K80" s="1">
         <v>46210.67465277778</v>
@@ -2671,10 +2691,10 @@
         <v>28</v>
       </c>
       <c r="E81">
-        <v>5554</v>
+        <v>4963</v>
       </c>
       <c r="F81" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>18</v>
@@ -2683,13 +2703,13 @@
         <v>10</v>
       </c>
       <c r="J81" s="2">
-        <v>7.0717592592592594E-3</v>
+        <v>6.1689814814814819E-3</v>
       </c>
       <c r="K81" s="1">
-        <v>46210.67465277778</v>
+        <v>46210.675347222219</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="s">
         <v>11</v>
@@ -2700,10 +2720,10 @@
         <v>28</v>
       </c>
       <c r="E82">
-        <v>4963</v>
+        <v>5558</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>18</v>
@@ -2712,13 +2732,13 @@
         <v>10</v>
       </c>
       <c r="J82" s="2">
-        <v>6.1689814814814819E-3</v>
+        <v>8.2060185185185187E-3</v>
       </c>
       <c r="K82" s="1">
-        <v>46210.675347222219</v>
+        <v>46210.676041666666</v>
       </c>
       <c r="L82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="s">
         <v>11</v>
@@ -2729,10 +2749,10 @@
         <v>28</v>
       </c>
       <c r="E83">
-        <v>5558</v>
+        <v>5559</v>
       </c>
       <c r="F83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>18</v>
@@ -2741,10 +2761,10 @@
         <v>10</v>
       </c>
       <c r="J83" s="2">
-        <v>8.2060185185185187E-3</v>
+        <v>7.1064814814814819E-3</v>
       </c>
       <c r="K83" s="1">
-        <v>46210.676041666666</v>
+        <v>46210.676736111112</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -2758,10 +2778,10 @@
         <v>28</v>
       </c>
       <c r="E84">
-        <v>5559</v>
+        <v>5932</v>
       </c>
       <c r="F84" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>18</v>
@@ -2770,10 +2790,10 @@
         <v>10</v>
       </c>
       <c r="J84" s="2">
-        <v>7.1064814814814819E-3</v>
+        <v>6.9675925925925929E-3</v>
       </c>
       <c r="K84" s="1">
-        <v>46210.676736111112</v>
+        <v>46210.677430555559</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -2787,10 +2807,10 @@
         <v>28</v>
       </c>
       <c r="E85">
-        <v>5932</v>
+        <v>5560</v>
       </c>
       <c r="F85" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>18</v>
@@ -2799,7 +2819,7 @@
         <v>10</v>
       </c>
       <c r="J85" s="2">
-        <v>6.9675925925925929E-3</v>
+        <v>7.7546296296296295E-3</v>
       </c>
       <c r="K85" s="1">
         <v>46210.677430555559</v>
@@ -2816,66 +2836,66 @@
         <v>28</v>
       </c>
       <c r="E86">
-        <v>5560</v>
+        <v>5944</v>
       </c>
       <c r="F86" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J86" s="2">
-        <v>7.7546296296296295E-3</v>
+        <v>1.8668981481481481E-2</v>
       </c>
       <c r="K86" s="1">
-        <v>46210.677430555559</v>
+        <v>46210.678124999999</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D87" t="s">
+      <c r="H87" s="2"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="1"/>
+      <c r="M87" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D88" t="s">
         <v>28</v>
       </c>
-      <c r="E87">
-        <v>5944</v>
-      </c>
-      <c r="F87" t="s">
-        <v>50</v>
-      </c>
-      <c r="H87" s="2" t="s">
+      <c r="E88">
+        <v>5561</v>
+      </c>
+      <c r="F88" t="s">
+        <v>43</v>
+      </c>
+      <c r="H88" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J87" s="2">
-        <v>1.8668981481481481E-2</v>
-      </c>
-      <c r="K87" s="1">
-        <v>46210.678124999999</v>
-      </c>
-      <c r="L87">
-        <v>1</v>
-      </c>
-      <c r="M87" t="s">
+      <c r="I88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J88" s="2">
+        <v>8.6574074074074071E-3</v>
+      </c>
+      <c r="K88" s="1">
+        <v>46210.678819444445</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H88" s="2"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="1"/>
-      <c r="M88" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
@@ -2883,10 +2903,10 @@
         <v>28</v>
       </c>
       <c r="E89">
-        <v>5561</v>
+        <v>5563</v>
       </c>
       <c r="F89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>18</v>
@@ -2895,10 +2915,10 @@
         <v>10</v>
       </c>
       <c r="J89" s="2">
-        <v>8.6574074074074071E-3</v>
+        <v>5.9722222222222225E-3</v>
       </c>
       <c r="K89" s="1">
-        <v>46210.678819444445</v>
+        <v>46210.680208333331</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -2912,10 +2932,10 @@
         <v>28</v>
       </c>
       <c r="E90">
-        <v>5563</v>
+        <v>5568</v>
       </c>
       <c r="F90" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>18</v>
@@ -2924,10 +2944,10 @@
         <v>10</v>
       </c>
       <c r="J90" s="2">
-        <v>5.9722222222222225E-3</v>
+        <v>6.3888888888888893E-3</v>
       </c>
       <c r="K90" s="1">
-        <v>46210.680208333331</v>
+        <v>46210.680902777778</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -2941,10 +2961,10 @@
         <v>28</v>
       </c>
       <c r="E91">
-        <v>5568</v>
+        <v>5566</v>
       </c>
       <c r="F91" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>18</v>
@@ -2953,7 +2973,7 @@
         <v>10</v>
       </c>
       <c r="J91" s="2">
-        <v>6.3888888888888893E-3</v>
+        <v>5.9837962962962961E-3</v>
       </c>
       <c r="K91" s="1">
         <v>46210.680902777778</v>
@@ -2970,10 +2990,10 @@
         <v>28</v>
       </c>
       <c r="E92">
-        <v>5566</v>
+        <v>5565</v>
       </c>
       <c r="F92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>18</v>
@@ -2982,10 +3002,10 @@
         <v>10</v>
       </c>
       <c r="J92" s="2">
-        <v>5.9837962962962961E-3</v>
+        <v>6.7824074074074071E-3</v>
       </c>
       <c r="K92" s="1">
-        <v>46210.680902777778</v>
+        <v>46210.681597222225</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -2995,33 +3015,10 @@
       </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D93" t="s">
-        <v>28</v>
-      </c>
-      <c r="E93">
-        <v>5565</v>
-      </c>
-      <c r="F93" t="s">
-        <v>47</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J93" s="2">
-        <v>6.7824074074074071E-3</v>
-      </c>
-      <c r="K93" s="1">
-        <v>46210.681597222225</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93" t="s">
-        <v>11</v>
-      </c>
+      <c r="H93" s="2"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="1"/>
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H94" s="2"/>
@@ -5294,6 +5291,7 @@
     <row r="472" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H472" s="2"/>
       <c r="I472" s="1"/>
+      <c r="J472" s="2"/>
       <c r="K472" s="1"/>
     </row>
     <row r="473" spans="8:11" x14ac:dyDescent="0.3">
@@ -6642,6 +6640,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -6951,6 +6950,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -7040,6 +7040,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -7146,6 +7147,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -7163,6 +7165,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -7174,6 +7177,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -7215,6 +7219,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -7238,6 +7243,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -7261,6 +7267,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -7278,6 +7285,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -7289,11 +7297,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -7413,6 +7423,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -7496,6 +7507,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -7519,6 +7531,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -7530,6 +7543,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -7541,6 +7555,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -7588,6 +7603,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -7641,6 +7657,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -7813,6 +7830,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -7824,6 +7842,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -7901,6 +7920,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -7918,6 +7938,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -7965,6 +7986,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -8077,6 +8099,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -8136,6 +8159,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -8147,6 +8171,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -8218,6 +8243,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -8270,6 +8296,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -8346,11 +8373,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -8410,6 +8439,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -8421,6 +8451,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -8432,11 +8463,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -8490,6 +8523,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -8506,6 +8540,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -8529,6 +8564,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -8546,6 +8582,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -8592,11 +8629,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -8638,11 +8677,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -8660,6 +8701,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -8671,6 +8713,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -8682,6 +8725,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -8699,6 +8743,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -8776,6 +8821,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -8805,6 +8851,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -8816,16 +8863,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -8837,16 +8887,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -8858,11 +8911,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -8886,6 +8941,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -8927,6 +8983,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -8956,21 +9013,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -8982,6 +9043,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -8999,6 +9061,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -9038,11 +9101,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -9090,6 +9155,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -9119,6 +9185,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -9195,6 +9262,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -9241,6 +9309,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -9276,11 +9345,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -9297,6 +9368,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -9307,6 +9379,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -9342,6 +9415,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -9353,6 +9427,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -9364,6 +9439,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -9375,6 +9451,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -9386,6 +9463,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -9427,6 +9505,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -9444,6 +9523,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -9461,6 +9541,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -9502,6 +9583,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -9525,6 +9607,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -9571,6 +9654,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -9606,6 +9690,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -9629,6 +9714,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -9669,6 +9755,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -9686,11 +9773,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -9749,6 +9838,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -9765,6 +9855,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -9776,6 +9867,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -9787,11 +9879,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -9827,6 +9921,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -9879,6 +9974,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -9889,6 +9985,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -9904,6 +10001,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -9927,16 +10025,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -10007,6 +10108,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -10018,6 +10120,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -10118,6 +10221,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -10174,6 +10279,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -10197,6 +10303,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -10321,6 +10428,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -10479,6 +10587,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -10496,6 +10605,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -10536,6 +10646,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -10868,6 +10979,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -10956,6 +11068,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -11049,6 +11162,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -11108,11 +11222,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -11164,6 +11280,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -11205,6 +11322,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -11249,6 +11367,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -11295,11 +11414,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -11497,6 +11618,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -11526,6 +11648,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -11541,6 +11665,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -11600,6 +11725,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -11671,6 +11797,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -11712,6 +11839,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -11830,6 +11958,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -11894,6 +12023,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -12018,6 +12148,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -12244,6 +12375,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -12361,6 +12493,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -12444,6 +12577,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -12503,6 +12637,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -12526,6 +12661,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -12573,6 +12709,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -12632,6 +12769,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -12655,6 +12793,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -12672,6 +12811,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -12755,6 +12895,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -12946,6 +13087,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -40802,6 +40944,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -40809,6 +40952,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -40816,6 +40960,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -40831,6 +40976,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -40840,6 +40986,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -40847,9 +40994,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -40857,12 +41010,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -40870,12 +41026,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -40887,9 +41046,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -40904,6 +41065,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -40930,6 +41092,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -40940,7 +41103,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -40948,6 +41116,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -40959,6 +41128,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -40966,6 +41136,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -40980,13 +41151,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -40997,15 +41174,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -41021,6 +41201,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -41039,6 +41220,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -41050,6 +41232,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -41067,18 +41250,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -41107,6 +41295,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -41114,9 +41303,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -41139,12 +41330,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -41159,9 +41353,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -41177,12 +41373,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -41203,6 +41401,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -41214,9 +41413,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -41228,6 +41429,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -41267,9 +41469,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -41277,9 +41481,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -41290,6 +41496,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -41297,18 +41504,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -41316,6 +41531,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -41326,6 +41542,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -41352,15 +41569,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -41382,6 +41603,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -41389,9 +41611,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -41399,6 +41623,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -41410,6 +41635,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -41424,6 +41650,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -41433,6 +41663,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -41444,6 +41675,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -41454,10 +41686,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -41465,6 +41702,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -41479,6 +41717,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -41501,6 +41740,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -41520,25 +41760,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -41546,6 +41798,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -41553,15 +41806,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -41575,6 +41835,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -41593,9 +41854,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -41603,9 +41866,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -41613,6 +41878,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -41629,10 +41895,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Brads-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E9E6926-1AD2-4929-9FAE-EF20C126353E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E958B156-2BF0-434A-9BD2-01AB5C28731C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="52">
   <si>
     <t>Company Name</t>
   </si>
@@ -119,13 +119,7 @@
     <t>Austin Simms</t>
   </si>
   <si>
-    <t>Chase Bennett</t>
-  </si>
-  <si>
     <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Brad's Towing</t>
@@ -188,16 +182,19 @@
     <t>Tyler Schliefert</t>
   </si>
   <si>
+    <t>Chase Bennett</t>
+  </si>
+  <si>
     <t>Brad Jackmane</t>
   </si>
   <si>
     <t>Erika</t>
   </si>
   <si>
-    <t>Kenny Purdue</t>
+    <t>Josh Dobney</t>
   </si>
   <si>
-    <t>Josh Dobney</t>
+    <t>Kenny Purdue</t>
   </si>
 </sst>
 </file>
@@ -571,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -586,47 +583,47 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>4962</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -647,15 +644,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>4964</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -676,7 +673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H4" s="2"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2"/>
@@ -684,15 +681,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>4965</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -713,15 +710,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>4963</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -742,15 +739,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>4962</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -771,15 +768,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>4964</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
@@ -800,7 +797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -808,15 +805,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>4965</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
@@ -837,15 +834,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>4963</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
@@ -866,15 +863,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>4962</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -895,15 +892,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13">
         <v>4965</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -924,15 +921,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>4963</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -953,7 +950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2"/>
@@ -961,15 +958,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>4962</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
@@ -1000,13 +997,13 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C18">
         <v>4965</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
@@ -1029,13 +1026,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>4963</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
         <v>22</v>
@@ -1058,13 +1055,13 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C20">
         <v>4962</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
@@ -1087,13 +1084,13 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <v>4965</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
@@ -1116,13 +1113,13 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>4963</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
@@ -1145,7 +1142,7 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C23">
         <v>5570</v>
@@ -1174,13 +1171,13 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C24">
         <v>5569</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
@@ -1203,13 +1200,13 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>5553</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
         <v>17</v>
@@ -1240,13 +1237,13 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <v>5571</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
@@ -1269,13 +1266,13 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C28">
         <v>5555</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F28" t="s">
         <v>17</v>
@@ -1298,13 +1295,13 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C29">
         <v>5556</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F29" t="s">
         <v>17</v>
@@ -1335,13 +1332,13 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C31">
         <v>5557</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s">
         <v>17</v>
@@ -1364,13 +1361,13 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C32">
         <v>5554</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
@@ -1401,13 +1398,13 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C34">
         <v>5558</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F34" t="s">
         <v>17</v>
@@ -1438,13 +1435,13 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C36">
         <v>5559</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
@@ -1467,13 +1464,13 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37">
         <v>5560</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F37" t="s">
         <v>17</v>
@@ -1496,13 +1493,13 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C38">
         <v>5561</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
@@ -1525,13 +1522,13 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C39">
         <v>5563</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F39" t="s">
         <v>17</v>
@@ -1554,13 +1551,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C40">
         <v>5568</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
         <v>17</v>
@@ -1583,13 +1580,13 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C41">
         <v>5566</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
@@ -1612,13 +1609,13 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C42">
         <v>5565</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F42" t="s">
         <v>17</v>
@@ -1641,13 +1638,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C43">
         <v>5662</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F43" t="s">
         <v>17</v>
@@ -1670,16 +1667,16 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C44">
         <v>5556</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G44" t="s">
         <v>10</v>
@@ -1699,16 +1696,16 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C45">
         <v>5749</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G45" t="s">
         <v>13</v>
@@ -1728,16 +1725,16 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C46">
         <v>5748</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G46" t="s">
         <v>13</v>
@@ -1757,13 +1754,13 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C47">
         <v>5749</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
@@ -1786,13 +1783,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C48">
         <v>5560</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
@@ -1815,13 +1812,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C49">
         <v>5565</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -1844,13 +1841,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C50">
         <v>4962</v>
       </c>
       <c r="D50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F50" t="s">
         <v>23</v>
@@ -1873,13 +1870,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C51">
         <v>5569</v>
       </c>
       <c r="D51" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F51" t="s">
         <v>23</v>
@@ -1910,13 +1907,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C53">
         <v>5553</v>
       </c>
       <c r="D53" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
         <v>23</v>
@@ -1939,13 +1936,13 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C54">
         <v>5571</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F54" t="s">
         <v>23</v>
@@ -1968,13 +1965,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C55">
         <v>5555</v>
       </c>
       <c r="D55" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F55" t="s">
         <v>23</v>
@@ -1997,13 +1994,13 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C56">
-        <v>5748</v>
+        <v>5556</v>
       </c>
       <c r="D56" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F56" t="s">
         <v>23</v>
@@ -2015,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="1">
-        <v>46175.8</v>
+        <v>46175.800694444442</v>
       </c>
       <c r="J56" s="2">
         <v>1</v>
@@ -2026,13 +2023,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C57">
-        <v>5556</v>
+        <v>5557</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F57" t="s">
         <v>23</v>
@@ -2044,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="1">
-        <v>46175.800694444442</v>
+        <v>46175.801388888889</v>
       </c>
       <c r="J57" s="2">
         <v>1</v>
@@ -2055,13 +2052,13 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C58">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="D58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
         <v>23</v>
@@ -2073,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="1">
-        <v>46175.801388888889</v>
+        <v>46175.802083333336</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
@@ -2084,13 +2081,13 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C59">
-        <v>5554</v>
+        <v>4963</v>
       </c>
       <c r="D59" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F59" t="s">
         <v>23</v>
@@ -2113,28 +2110,28 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C60">
-        <v>4963</v>
+        <v>5558</v>
       </c>
       <c r="D60" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F60" t="s">
         <v>23</v>
       </c>
       <c r="G60" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H60" s="2">
-        <v>0</v>
+        <v>1.1631944444444445E-2</v>
       </c>
       <c r="I60" s="1">
-        <v>46175.802083333336</v>
+        <v>46175.802777777775</v>
       </c>
       <c r="J60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>11</v>
@@ -2142,28 +2139,28 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C61">
-        <v>5558</v>
+        <v>5559</v>
       </c>
       <c r="D61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
       </c>
       <c r="G61" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H61" s="2">
-        <v>1.1631944444444445E-2</v>
+        <v>0</v>
       </c>
       <c r="I61" s="1">
-        <v>46175.802777777775</v>
+        <v>46175.803472222222</v>
       </c>
       <c r="J61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>11</v>
@@ -2171,10 +2168,10 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C62">
-        <v>5559</v>
+        <v>5561</v>
       </c>
       <c r="D62" t="s">
         <v>42</v>
@@ -2183,13 +2180,13 @@
         <v>23</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H62" s="2">
-        <v>0</v>
+        <v>9.5370370370370366E-3</v>
       </c>
       <c r="I62" s="1">
-        <v>46175.803472222222</v>
+        <v>46175.804166666669</v>
       </c>
       <c r="J62" s="2">
         <v>1</v>
@@ -2200,25 +2197,25 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C63">
-        <v>5561</v>
+        <v>5563</v>
       </c>
       <c r="D63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F63" t="s">
         <v>23</v>
       </c>
       <c r="G63" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H63" s="2">
-        <v>9.5370370370370366E-3</v>
+        <v>0</v>
       </c>
       <c r="I63" s="1">
-        <v>46175.804166666669</v>
+        <v>46175.804861111108</v>
       </c>
       <c r="J63" s="2">
         <v>1</v>
@@ -2229,13 +2226,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C64">
-        <v>5563</v>
+        <v>5568</v>
       </c>
       <c r="D64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F64" t="s">
         <v>23</v>
@@ -2258,25 +2255,25 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C65">
-        <v>5568</v>
+        <v>5566</v>
       </c>
       <c r="D65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F65" t="s">
         <v>23</v>
       </c>
       <c r="G65" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H65" s="2">
-        <v>0</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="I65" s="1">
-        <v>46175.804861111108</v>
+        <v>46175.805555555555</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
@@ -2287,91 +2284,91 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C66">
-        <v>5566</v>
+        <v>5558</v>
       </c>
       <c r="D66" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F66" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H66" s="2">
-        <v>6.9444444444444441E-3</v>
+        <v>1.8703703703703705E-2</v>
       </c>
       <c r="I66" s="1">
-        <v>46175.805555555555</v>
+        <v>46203.711111111108</v>
       </c>
       <c r="J66" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>29</v>
-      </c>
-      <c r="C67">
-        <v>5558</v>
-      </c>
-      <c r="D67" t="s">
-        <v>41</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="H67" s="2"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>27</v>
       </c>
-      <c r="G67" t="s">
-        <v>12</v>
-      </c>
-      <c r="H67" s="2">
-        <v>1.8703703703703705E-2</v>
-      </c>
-      <c r="I67" s="1">
-        <v>46203.711111111108</v>
-      </c>
-      <c r="J67" s="2">
-        <v>2</v>
-      </c>
-      <c r="K67" s="1" t="s">
+      <c r="C68">
+        <v>4962</v>
+      </c>
+      <c r="D68" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" s="2">
+        <v>5.5092592592592589E-3</v>
+      </c>
+      <c r="I68" s="1">
+        <v>46210.669791666667</v>
+      </c>
+      <c r="J68" s="2">
+        <v>1</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H68" s="2"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C69">
-        <v>5944</v>
+        <v>5569</v>
       </c>
       <c r="D69" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F69" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H69" s="2">
-        <v>1.5162037037037036E-3</v>
+        <v>5.3935185185185188E-3</v>
       </c>
       <c r="I69" s="1">
-        <v>46204.585648148146</v>
+        <v>46210.670486111114</v>
       </c>
       <c r="J69" s="2">
         <v>0</v>
@@ -2381,22 +2378,43 @@
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H70" s="2"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="2"/>
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70">
+        <v>5553</v>
+      </c>
+      <c r="D70" t="s">
+        <v>33</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+      <c r="H70" s="2">
+        <v>6.122685185185185E-3</v>
+      </c>
+      <c r="I70" s="1">
+        <v>46210.671875</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0</v>
+      </c>
       <c r="K70" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C71">
-        <v>4962</v>
+        <v>5571</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -2405,13 +2423,13 @@
         <v>10</v>
       </c>
       <c r="H71" s="2">
-        <v>5.5092592592592589E-3</v>
+        <v>1.3009259259259259E-2</v>
       </c>
       <c r="I71" s="1">
-        <v>46210.669791666667</v>
+        <v>46210.671875</v>
       </c>
       <c r="J71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>11</v>
@@ -2419,13 +2437,13 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C72">
-        <v>5569</v>
+        <v>5555</v>
       </c>
       <c r="D72" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
@@ -2434,10 +2452,10 @@
         <v>10</v>
       </c>
       <c r="H72" s="2">
-        <v>5.3935185185185188E-3</v>
+        <v>6.3078703703703708E-3</v>
       </c>
       <c r="I72" s="1">
-        <v>46210.670486111114</v>
+        <v>46210.672569444447</v>
       </c>
       <c r="J72" s="2">
         <v>0</v>
@@ -2448,28 +2466,28 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C73">
-        <v>5749</v>
+        <v>5556</v>
       </c>
       <c r="D73" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F73" t="s">
         <v>18</v>
       </c>
       <c r="G73" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H73" s="2">
-        <v>0</v>
+        <v>6.7476851851851856E-3</v>
       </c>
       <c r="I73" s="1">
-        <v>46210.671180555553</v>
+        <v>46210.673958333333</v>
       </c>
       <c r="J73" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K73" s="1" t="s">
         <v>11</v>
@@ -2477,13 +2495,13 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C74">
-        <v>5553</v>
+        <v>5557</v>
       </c>
       <c r="D74" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F74" t="s">
         <v>18</v>
@@ -2492,10 +2510,10 @@
         <v>10</v>
       </c>
       <c r="H74" s="2">
-        <v>6.122685185185185E-3</v>
+        <v>2.3333333333333334E-2</v>
       </c>
       <c r="I74" s="1">
-        <v>46210.671875</v>
+        <v>46210.67465277778</v>
       </c>
       <c r="J74" s="2">
         <v>0</v>
@@ -2506,13 +2524,13 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C75">
-        <v>5571</v>
+        <v>5554</v>
       </c>
       <c r="D75" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F75" t="s">
         <v>18</v>
@@ -2521,10 +2539,10 @@
         <v>10</v>
       </c>
       <c r="H75" s="2">
-        <v>1.3009259259259259E-2</v>
+        <v>7.0717592592592594E-3</v>
       </c>
       <c r="I75" s="1">
-        <v>46210.671875</v>
+        <v>46210.67465277778</v>
       </c>
       <c r="J75" s="2">
         <v>0</v>
@@ -2535,13 +2553,13 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C76">
-        <v>5555</v>
+        <v>4963</v>
       </c>
       <c r="D76" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F76" t="s">
         <v>18</v>
@@ -2550,13 +2568,13 @@
         <v>10</v>
       </c>
       <c r="H76" s="2">
-        <v>6.3078703703703708E-3</v>
+        <v>6.1689814814814819E-3</v>
       </c>
       <c r="I76" s="1">
-        <v>46210.672569444447</v>
+        <v>46210.675347222219</v>
       </c>
       <c r="J76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>11</v>
@@ -2564,28 +2582,28 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C77">
-        <v>5748</v>
+        <v>5558</v>
       </c>
       <c r="D77" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F77" t="s">
         <v>18</v>
       </c>
       <c r="G77" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H77" s="2">
+        <v>8.2060185185185187E-3</v>
+      </c>
+      <c r="I77" s="1">
+        <v>46210.676041666666</v>
+      </c>
+      <c r="J77" s="2">
         <v>0</v>
-      </c>
-      <c r="I77" s="1">
-        <v>46210.673263888886</v>
-      </c>
-      <c r="J77" s="2">
-        <v>2</v>
       </c>
       <c r="K77" s="1" t="s">
         <v>11</v>
@@ -2593,13 +2611,13 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C78">
-        <v>5556</v>
+        <v>5559</v>
       </c>
       <c r="D78" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F78" t="s">
         <v>18</v>
@@ -2608,13 +2626,13 @@
         <v>10</v>
       </c>
       <c r="H78" s="2">
-        <v>6.7476851851851856E-3</v>
+        <v>7.1064814814814819E-3</v>
       </c>
       <c r="I78" s="1">
-        <v>46210.673958333333</v>
+        <v>46210.676736111112</v>
       </c>
       <c r="J78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>11</v>
@@ -2622,13 +2640,13 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C79">
-        <v>5557</v>
+        <v>5932</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F79" t="s">
         <v>18</v>
@@ -2637,10 +2655,10 @@
         <v>10</v>
       </c>
       <c r="H79" s="2">
-        <v>2.3333333333333334E-2</v>
+        <v>6.9675925925925929E-3</v>
       </c>
       <c r="I79" s="1">
-        <v>46210.67465277778</v>
+        <v>46210.677430555559</v>
       </c>
       <c r="J79" s="2">
         <v>0</v>
@@ -2651,13 +2669,13 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C80">
-        <v>5554</v>
+        <v>5560</v>
       </c>
       <c r="D80" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F80" t="s">
         <v>18</v>
@@ -2666,10 +2684,10 @@
         <v>10</v>
       </c>
       <c r="H80" s="2">
-        <v>7.0717592592592594E-3</v>
+        <v>7.7546296296296295E-3</v>
       </c>
       <c r="I80" s="1">
-        <v>46210.67465277778</v>
+        <v>46210.677430555559</v>
       </c>
       <c r="J80" s="2">
         <v>0</v>
@@ -2680,68 +2698,47 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C81">
-        <v>4963</v>
+        <v>5944</v>
       </c>
       <c r="D81" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F81" t="s">
         <v>18</v>
       </c>
       <c r="G81" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H81" s="2">
-        <v>6.1689814814814819E-3</v>
+        <v>1.8668981481481481E-2</v>
       </c>
       <c r="I81" s="1">
-        <v>46210.675347222219</v>
+        <v>46210.678124999999</v>
       </c>
       <c r="J81" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K81" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>29</v>
-      </c>
-      <c r="C82">
-        <v>5558</v>
-      </c>
-      <c r="D82" t="s">
-        <v>41</v>
-      </c>
-      <c r="F82" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" t="s">
-        <v>10</v>
-      </c>
-      <c r="H82" s="2">
-        <v>8.2060185185185187E-3</v>
-      </c>
-      <c r="I82" s="1">
-        <v>46210.676041666666</v>
-      </c>
-      <c r="J82" s="2">
-        <v>0</v>
-      </c>
+      <c r="H82" s="2"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="2"/>
       <c r="K82" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C83">
-        <v>5559</v>
+        <v>5561</v>
       </c>
       <c r="D83" t="s">
         <v>42</v>
@@ -2753,10 +2750,10 @@
         <v>10</v>
       </c>
       <c r="H83" s="2">
-        <v>7.1064814814814819E-3</v>
+        <v>8.6574074074074071E-3</v>
       </c>
       <c r="I83" s="1">
-        <v>46210.676736111112</v>
+        <v>46210.678819444445</v>
       </c>
       <c r="J83" s="2">
         <v>0</v>
@@ -2767,13 +2764,13 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C84">
-        <v>5932</v>
+        <v>5563</v>
       </c>
       <c r="D84" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F84" t="s">
         <v>18</v>
@@ -2782,10 +2779,10 @@
         <v>10</v>
       </c>
       <c r="H84" s="2">
-        <v>6.9675925925925929E-3</v>
+        <v>5.9722222222222225E-3</v>
       </c>
       <c r="I84" s="1">
-        <v>46210.677430555559</v>
+        <v>46210.680208333331</v>
       </c>
       <c r="J84" s="2">
         <v>0</v>
@@ -2796,13 +2793,13 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C85">
-        <v>5560</v>
+        <v>5568</v>
       </c>
       <c r="D85" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F85" t="s">
         <v>18</v>
@@ -2811,10 +2808,10 @@
         <v>10</v>
       </c>
       <c r="H85" s="2">
-        <v>7.7546296296296295E-3</v>
+        <v>6.3888888888888893E-3</v>
       </c>
       <c r="I85" s="1">
-        <v>46210.677430555559</v>
+        <v>46210.680902777778</v>
       </c>
       <c r="J85" s="2">
         <v>0</v>
@@ -2825,62 +2822,83 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C86">
-        <v>5944</v>
+        <v>5566</v>
       </c>
       <c r="D86" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F86" t="s">
         <v>18</v>
       </c>
       <c r="G86" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H86" s="2">
-        <v>1.8668981481481481E-2</v>
+        <v>5.9837962962962961E-3</v>
       </c>
       <c r="I86" s="1">
-        <v>46210.678124999999</v>
+        <v>46210.680902777778</v>
       </c>
       <c r="J86" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H87" s="2"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="2"/>
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87">
+        <v>5565</v>
+      </c>
+      <c r="D87" t="s">
+        <v>46</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="2">
+        <v>6.7824074074074071E-3</v>
+      </c>
+      <c r="I87" s="1">
+        <v>46210.681597222225</v>
+      </c>
+      <c r="J87" s="2">
+        <v>0</v>
+      </c>
       <c r="K87" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C88">
-        <v>5561</v>
+        <v>4962</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F88" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G88" t="s">
         <v>10</v>
       </c>
       <c r="H88" s="2">
-        <v>8.6574074074074071E-3</v>
+        <v>1.1643518518518518E-2</v>
       </c>
       <c r="I88" s="1">
-        <v>46210.678819444445</v>
+        <v>46237.68854166667</v>
       </c>
       <c r="J88" s="2">
         <v>0</v>
@@ -2891,25 +2909,25 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C89">
-        <v>5563</v>
+        <v>5569</v>
       </c>
       <c r="D89" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F89" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G89" t="s">
         <v>10</v>
       </c>
       <c r="H89" s="2">
-        <v>5.9722222222222225E-3</v>
+        <v>5.2893518518518515E-3</v>
       </c>
       <c r="I89" s="1">
-        <v>46210.680208333331</v>
+        <v>46237.68854166667</v>
       </c>
       <c r="J89" s="2">
         <v>0</v>
@@ -2920,25 +2938,25 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C90">
-        <v>5568</v>
+        <v>5749</v>
       </c>
       <c r="D90" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F90" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G90" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H90" s="2">
-        <v>6.3888888888888893E-3</v>
+        <v>0</v>
       </c>
       <c r="I90" s="1">
-        <v>46210.680902777778</v>
+        <v>46237.689236111109</v>
       </c>
       <c r="J90" s="2">
         <v>0</v>
@@ -2949,28 +2967,28 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C91">
-        <v>5566</v>
+        <v>5553</v>
       </c>
       <c r="D91" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F91" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G91" t="s">
         <v>10</v>
       </c>
       <c r="H91" s="2">
-        <v>5.9837962962962961E-3</v>
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="I91" s="1">
-        <v>46210.680902777778</v>
+        <v>46237.689930555556</v>
       </c>
       <c r="J91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" s="1" t="s">
         <v>11</v>
@@ -2978,25 +2996,25 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C92">
-        <v>5565</v>
+        <v>5571</v>
       </c>
       <c r="D92" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F92" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G92" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H92" s="2">
-        <v>6.7824074074074071E-3</v>
+        <v>1.1574074074074075E-4</v>
       </c>
       <c r="I92" s="1">
-        <v>46210.681597222225</v>
+        <v>46237.689930555556</v>
       </c>
       <c r="J92" s="2">
         <v>0</v>
@@ -3006,63 +3024,63 @@
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>29</v>
-      </c>
-      <c r="C93">
-        <v>4962</v>
-      </c>
-      <c r="D93" t="s">
-        <v>30</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="H93" s="2"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94">
+        <v>5555</v>
+      </c>
+      <c r="D94" t="s">
+        <v>35</v>
+      </c>
+      <c r="F94" t="s">
         <v>24</v>
       </c>
-      <c r="G93" t="s">
-        <v>12</v>
-      </c>
-      <c r="H93" s="2">
-        <v>2.9976851851851853E-3</v>
-      </c>
-      <c r="I93" s="1">
-        <v>46237.68854166667</v>
-      </c>
-      <c r="J93" s="2">
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" s="2">
+        <v>7.037037037037037E-3</v>
+      </c>
+      <c r="I94" s="1">
+        <v>46237.690625000003</v>
+      </c>
+      <c r="J94" s="2">
         <v>0</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H94" s="2"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C95">
-        <v>5569</v>
+        <v>5556</v>
       </c>
       <c r="D95" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F95" t="s">
         <v>24</v>
       </c>
       <c r="G95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H95" s="2">
-        <v>0</v>
+        <v>7.951388888888888E-3</v>
       </c>
       <c r="I95" s="1">
-        <v>46237.68854166667</v>
+        <v>46237.692013888889</v>
       </c>
       <c r="J95" s="2">
         <v>0</v>
@@ -3072,43 +3090,22 @@
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>29</v>
-      </c>
-      <c r="C96">
-        <v>5749</v>
-      </c>
-      <c r="D96" t="s">
-        <v>49</v>
-      </c>
-      <c r="F96" t="s">
-        <v>24</v>
-      </c>
-      <c r="G96" t="s">
-        <v>13</v>
-      </c>
-      <c r="H96" s="2">
-        <v>0</v>
-      </c>
-      <c r="I96" s="1">
-        <v>46237.689236111109</v>
-      </c>
-      <c r="J96" s="2">
-        <v>0</v>
-      </c>
+      <c r="H96" s="2"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="2"/>
       <c r="K96" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C97">
-        <v>5553</v>
+        <v>5557</v>
       </c>
       <c r="D97" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F97" t="s">
         <v>24</v>
@@ -3120,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="1">
-        <v>46237.689930555556</v>
+        <v>46237.669212962966</v>
       </c>
       <c r="J97" s="2">
         <v>0</v>
@@ -3131,13 +3128,13 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C98">
-        <v>5571</v>
+        <v>5554</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F98" t="s">
         <v>24</v>
@@ -3149,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="1">
-        <v>46237.689930555556</v>
+        <v>46237.669212962966</v>
       </c>
       <c r="J98" s="2">
         <v>0</v>
@@ -3160,25 +3157,25 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C99">
-        <v>5555</v>
+        <v>4963</v>
       </c>
       <c r="D99" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F99" t="s">
         <v>24</v>
       </c>
       <c r="G99" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H99" s="2">
-        <v>1.0416666666666667E-4</v>
+        <v>6.0069444444444441E-3</v>
       </c>
       <c r="I99" s="1">
-        <v>46237.690625000003</v>
+        <v>46237.669907407406</v>
       </c>
       <c r="J99" s="2">
         <v>0</v>
@@ -3188,34 +3185,55 @@
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H100" s="2"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="2"/>
+      <c r="B100" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100">
+        <v>5558</v>
+      </c>
+      <c r="D100" t="s">
+        <v>39</v>
+      </c>
+      <c r="F100" t="s">
+        <v>24</v>
+      </c>
+      <c r="G100" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="2">
+        <v>8.9236111111111113E-3</v>
+      </c>
+      <c r="I100" s="1">
+        <v>46237.670601851853</v>
+      </c>
+      <c r="J100" s="2">
+        <v>0</v>
+      </c>
       <c r="K100" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C101">
-        <v>5748</v>
+        <v>5559</v>
       </c>
       <c r="D101" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F101" t="s">
         <v>24</v>
       </c>
       <c r="G101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H101" s="2">
-        <v>0</v>
+        <v>1.1574074074074075E-4</v>
       </c>
       <c r="I101" s="1">
-        <v>46237.691319444442</v>
+        <v>46237.670601851853</v>
       </c>
       <c r="J101" s="2">
         <v>0</v>
@@ -3225,55 +3243,34 @@
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B102" t="s">
-        <v>29</v>
-      </c>
-      <c r="C102">
-        <v>5556</v>
-      </c>
-      <c r="D102" t="s">
-        <v>38</v>
-      </c>
-      <c r="F102" t="s">
-        <v>24</v>
-      </c>
-      <c r="G102" t="s">
-        <v>13</v>
-      </c>
-      <c r="H102" s="2">
-        <v>0</v>
-      </c>
-      <c r="I102" s="1">
-        <v>46237.692013888889</v>
-      </c>
-      <c r="J102" s="2">
-        <v>0</v>
-      </c>
+      <c r="H102" s="2"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="2"/>
       <c r="K102" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C103">
-        <v>5557</v>
+        <v>5932</v>
       </c>
       <c r="D103" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F103" t="s">
         <v>24</v>
       </c>
       <c r="G103" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H103" s="2">
-        <v>0</v>
+        <v>8.2060185185185187E-3</v>
       </c>
       <c r="I103" s="1">
-        <v>46237.669212962966</v>
+        <v>46237.671296296299</v>
       </c>
       <c r="J103" s="2">
         <v>0</v>
@@ -3284,25 +3281,25 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C104">
-        <v>5554</v>
+        <v>5560</v>
       </c>
       <c r="D104" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F104" t="s">
         <v>24</v>
       </c>
       <c r="G104" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H104" s="2">
-        <v>0</v>
+        <v>6.7361111111111111E-3</v>
       </c>
       <c r="I104" s="1">
-        <v>46237.669212962966</v>
+        <v>46237.671296296299</v>
       </c>
       <c r="J104" s="2">
         <v>0</v>
@@ -3313,13 +3310,13 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C105">
-        <v>4963</v>
+        <v>5944</v>
       </c>
       <c r="D105" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F105" t="s">
         <v>24</v>
@@ -3331,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="1">
-        <v>46237.669907407406</v>
+        <v>46237.671990740739</v>
       </c>
       <c r="J105" s="2">
         <v>0</v>
@@ -3342,13 +3339,13 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C106">
-        <v>5558</v>
+        <v>5561</v>
       </c>
       <c r="D106" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F106" t="s">
         <v>24</v>
@@ -3360,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="1">
-        <v>46237.670601851853</v>
+        <v>46237.672685185185</v>
       </c>
       <c r="J106" s="2">
         <v>0</v>
@@ -3371,25 +3368,25 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C107">
-        <v>5559</v>
+        <v>5563</v>
       </c>
       <c r="D107" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F107" t="s">
         <v>24</v>
       </c>
       <c r="G107" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H107" s="2">
-        <v>0</v>
+        <v>6.3078703703703708E-3</v>
       </c>
       <c r="I107" s="1">
-        <v>46237.670601851853</v>
+        <v>46237.672685185185</v>
       </c>
       <c r="J107" s="2">
         <v>0</v>
@@ -3400,25 +3397,25 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C108">
-        <v>5932</v>
+        <v>5568</v>
       </c>
       <c r="D108" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F108" t="s">
         <v>24</v>
       </c>
       <c r="G108" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H108" s="2">
-        <v>8.1018518518518516E-5</v>
+        <v>8.3564814814814821E-3</v>
       </c>
       <c r="I108" s="1">
-        <v>46237.671296296299</v>
+        <v>46237.673379629632</v>
       </c>
       <c r="J108" s="2">
         <v>0</v>
@@ -3428,285 +3425,168 @@
       </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H109" s="2"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="2"/>
+      <c r="B109" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109">
+        <v>5566</v>
+      </c>
+      <c r="D109" t="s">
+        <v>45</v>
+      </c>
+      <c r="F109" t="s">
+        <v>24</v>
+      </c>
+      <c r="G109" t="s">
+        <v>12</v>
+      </c>
+      <c r="H109" s="2">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1">
+        <v>46237.674074074072</v>
+      </c>
+      <c r="J109" s="2">
+        <v>0</v>
+      </c>
       <c r="K109" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H110" s="2"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
-        <v>29</v>
-      </c>
-      <c r="C110">
-        <v>5560</v>
-      </c>
-      <c r="D110" t="s">
-        <v>43</v>
-      </c>
-      <c r="F110" t="s">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111">
+        <v>5565</v>
+      </c>
+      <c r="D111" t="s">
+        <v>46</v>
+      </c>
+      <c r="F111" t="s">
         <v>24</v>
       </c>
-      <c r="G110" t="s">
-        <v>12</v>
-      </c>
-      <c r="H110" s="2">
+      <c r="G111" t="s">
+        <v>10</v>
+      </c>
+      <c r="H111" s="2">
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="I111" s="1">
+        <v>46237.674074074072</v>
+      </c>
+      <c r="J111" s="2">
         <v>0</v>
       </c>
-      <c r="I110" s="1">
-        <v>46237.671296296299</v>
-      </c>
-      <c r="J110" s="2">
-        <v>0</v>
-      </c>
-      <c r="K110" s="1" t="s">
+      <c r="K111" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H111" s="2"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="2"/>
-      <c r="K111" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B112" t="s">
-        <v>29</v>
-      </c>
-      <c r="C112">
-        <v>5944</v>
-      </c>
-      <c r="D112" t="s">
-        <v>51</v>
-      </c>
-      <c r="F112" t="s">
-        <v>24</v>
-      </c>
-      <c r="G112" t="s">
-        <v>13</v>
-      </c>
-      <c r="H112" s="2">
-        <v>0</v>
-      </c>
-      <c r="I112" s="1">
-        <v>46237.671990740739</v>
-      </c>
-      <c r="J112" s="2">
-        <v>0</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B113" t="s">
-        <v>29</v>
-      </c>
-      <c r="C113">
-        <v>5561</v>
-      </c>
-      <c r="D113" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" t="s">
-        <v>24</v>
-      </c>
-      <c r="G113" t="s">
-        <v>13</v>
-      </c>
-      <c r="H113" s="2">
-        <v>0</v>
-      </c>
-      <c r="I113" s="1">
-        <v>46237.672685185185</v>
-      </c>
-      <c r="J113" s="2">
-        <v>0</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
-        <v>29</v>
-      </c>
-      <c r="C114">
-        <v>5563</v>
-      </c>
-      <c r="D114" t="s">
-        <v>45</v>
-      </c>
-      <c r="F114" t="s">
-        <v>24</v>
-      </c>
-      <c r="G114" t="s">
-        <v>13</v>
-      </c>
-      <c r="H114" s="2">
-        <v>0</v>
-      </c>
-      <c r="I114" s="1">
-        <v>46237.672685185185</v>
-      </c>
-      <c r="J114" s="2">
-        <v>0</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B115" t="s">
-        <v>29</v>
-      </c>
-      <c r="C115">
-        <v>5568</v>
-      </c>
-      <c r="D115" t="s">
-        <v>46</v>
-      </c>
-      <c r="F115" t="s">
-        <v>24</v>
-      </c>
-      <c r="G115" t="s">
-        <v>13</v>
-      </c>
-      <c r="H115" s="2">
-        <v>0</v>
-      </c>
-      <c r="I115" s="1">
-        <v>46237.673379629632</v>
-      </c>
-      <c r="J115" s="2">
-        <v>0</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B116" t="s">
-        <v>29</v>
-      </c>
-      <c r="C116">
-        <v>5566</v>
-      </c>
-      <c r="D116" t="s">
-        <v>47</v>
-      </c>
-      <c r="F116" t="s">
-        <v>24</v>
-      </c>
-      <c r="G116" t="s">
-        <v>13</v>
-      </c>
-      <c r="H116" s="2">
-        <v>0</v>
-      </c>
-      <c r="I116" s="1">
-        <v>46237.674074074072</v>
-      </c>
-      <c r="J116" s="2">
-        <v>0</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B117" t="s">
-        <v>29</v>
-      </c>
-      <c r="C117">
-        <v>5565</v>
-      </c>
-      <c r="D117" t="s">
-        <v>48</v>
-      </c>
-      <c r="F117" t="s">
-        <v>24</v>
-      </c>
-      <c r="G117" t="s">
-        <v>13</v>
-      </c>
-      <c r="H117" s="2">
-        <v>0</v>
-      </c>
-      <c r="I117" s="1">
-        <v>46237.674074074072</v>
-      </c>
-      <c r="J117" s="2">
-        <v>0</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H112" s="2"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="1"/>
+    </row>
+    <row r="113" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H113" s="2"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="2"/>
+      <c r="K113" s="1"/>
+    </row>
+    <row r="114" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H114" s="2"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="1"/>
+    </row>
+    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H115" s="2"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="1"/>
+    </row>
+    <row r="116" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H116" s="2"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="2"/>
+      <c r="K116" s="1"/>
+    </row>
+    <row r="117" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H117" s="2"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="1"/>
+    </row>
+    <row r="118" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H118" s="2"/>
       <c r="I118" s="1"/>
       <c r="J118" s="2"/>
       <c r="K118" s="1"/>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H119" s="2"/>
       <c r="I119" s="1"/>
       <c r="J119" s="2"/>
       <c r="K119" s="1"/>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H120" s="2"/>
       <c r="I120" s="1"/>
       <c r="J120" s="2"/>
       <c r="K120" s="1"/>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H121" s="2"/>
       <c r="I121" s="1"/>
       <c r="J121" s="2"/>
       <c r="K121" s="1"/>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H122" s="2"/>
       <c r="I122" s="1"/>
       <c r="J122" s="2"/>
       <c r="K122" s="1"/>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H123" s="2"/>
       <c r="I123" s="1"/>
       <c r="J123" s="2"/>
       <c r="K123" s="1"/>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H124" s="2"/>
       <c r="I124" s="1"/>
       <c r="J124" s="2"/>
       <c r="K124" s="1"/>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H125" s="2"/>
       <c r="I125" s="1"/>
       <c r="J125" s="2"/>
       <c r="K125" s="1"/>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H126" s="2"/>
       <c r="I126" s="1"/>
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H128" s="2"/>
       <c r="I128" s="1"/>
       <c r="J128" s="2"/>
@@ -45072,6 +44952,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -45086,11 +44967,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -45101,10 +44984,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -45122,14 +45008,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -45140,14 +45029,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -45174,6 +45066,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -45182,6 +45075,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -45194,22 +45088,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -45228,6 +45127,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -45238,10 +45138,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -45250,10 +45152,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -45267,82 +45171,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -45356,6 +45275,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -45366,6 +45286,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -45373,6 +45294,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -45381,86 +45303,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -45477,26 +45412,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -45527,6 +45468,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -45536,10 +45478,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -45552,14 +45496,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -45568,14 +45515,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -45594,26 +45544,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -45632,6 +45588,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -45640,10 +45597,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -45652,6 +45611,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -45664,10 +45624,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -45676,6 +45638,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -45684,14 +45647,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -45700,14 +45666,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -45724,76 +45693,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -45807,31 +45785,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -45844,10 +45829,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -45856,10 +45843,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -45868,6 +45857,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -45882,10 +45872,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -45894,10 +45886,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -45911,6 +45905,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -45926,14 +45921,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -45951,14 +45949,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -45971,10 +45972,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -45983,14 +45986,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -45999,10 +46005,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -46011,14 +46019,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -46040,6 +46051,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -46048,39 +46060,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Brads-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E958B156-2BF0-434A-9BD2-01AB5C28731C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03D275F3-7476-4CF2-B83D-FD5AC0CF6590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="52">
   <si>
     <t>Company Name</t>
   </si>
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -644,7 +644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>27</v>
       </c>
@@ -797,7 +797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -892,7 +892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1359,7 +1359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>27</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>27</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>27</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>27</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -2950,7 +2950,7 @@
         <v>24</v>
       </c>
       <c r="G90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
@@ -2959,76 +2959,76 @@
         <v>46237.689236111109</v>
       </c>
       <c r="J90" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K90" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>27</v>
-      </c>
-      <c r="C91">
-        <v>5553</v>
-      </c>
-      <c r="D91" t="s">
-        <v>33</v>
-      </c>
-      <c r="F91" t="s">
-        <v>24</v>
-      </c>
-      <c r="G91" t="s">
-        <v>10</v>
-      </c>
-      <c r="H91" s="2">
-        <v>1.3888888888888889E-4</v>
-      </c>
-      <c r="I91" s="1">
-        <v>46237.689930555556</v>
-      </c>
-      <c r="J91" s="2">
-        <v>1</v>
-      </c>
+      <c r="H91" s="2"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="2"/>
       <c r="K91" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>27</v>
       </c>
       <c r="C92">
-        <v>5571</v>
+        <v>5553</v>
       </c>
       <c r="D92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F92" t="s">
         <v>24</v>
       </c>
       <c r="G92" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H92" s="2">
-        <v>1.1574074074074075E-4</v>
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="I92" s="1">
         <v>46237.689930555556</v>
       </c>
       <c r="J92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H93" s="2"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="2"/>
+      <c r="B93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93">
+        <v>5571</v>
+      </c>
+      <c r="D93" t="s">
+        <v>34</v>
+      </c>
+      <c r="F93" t="s">
+        <v>24</v>
+      </c>
+      <c r="G93" t="s">
+        <v>10</v>
+      </c>
+      <c r="H93" s="2">
+        <v>9.3634259259259261E-3</v>
+      </c>
+      <c r="I93" s="1">
+        <v>46237.689930555556</v>
+      </c>
+      <c r="J93" s="2">
+        <v>1</v>
+      </c>
       <c r="K93" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
@@ -3083,7 +3083,7 @@
         <v>46237.692013888889</v>
       </c>
       <c r="J95" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>11</v>
@@ -3111,48 +3111,27 @@
         <v>24</v>
       </c>
       <c r="G97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H97" s="2">
-        <v>0</v>
+        <v>2.5462962962962961E-4</v>
       </c>
       <c r="I97" s="1">
         <v>46237.669212962966</v>
       </c>
       <c r="J97" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K97" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>27</v>
-      </c>
-      <c r="C98">
-        <v>5554</v>
-      </c>
-      <c r="D98" t="s">
-        <v>38</v>
-      </c>
-      <c r="F98" t="s">
-        <v>24</v>
-      </c>
-      <c r="G98" t="s">
-        <v>13</v>
-      </c>
-      <c r="H98" s="2">
-        <v>0</v>
-      </c>
-      <c r="I98" s="1">
-        <v>46237.669212962966</v>
-      </c>
-      <c r="J98" s="2">
-        <v>0</v>
-      </c>
+      <c r="H98" s="2"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="2"/>
       <c r="K98" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
@@ -3160,10 +3139,10 @@
         <v>27</v>
       </c>
       <c r="C99">
-        <v>4963</v>
+        <v>5554</v>
       </c>
       <c r="D99" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F99" t="s">
         <v>24</v>
@@ -3172,13 +3151,13 @@
         <v>10</v>
       </c>
       <c r="H99" s="2">
-        <v>6.0069444444444441E-3</v>
+        <v>6.053240740740741E-3</v>
       </c>
       <c r="I99" s="1">
-        <v>46237.669907407406</v>
+        <v>46237.669212962966</v>
       </c>
       <c r="J99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" s="1" t="s">
         <v>11</v>
@@ -3189,10 +3168,10 @@
         <v>27</v>
       </c>
       <c r="C100">
-        <v>5558</v>
+        <v>4963</v>
       </c>
       <c r="D100" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F100" t="s">
         <v>24</v>
@@ -3201,10 +3180,10 @@
         <v>10</v>
       </c>
       <c r="H100" s="2">
-        <v>8.9236111111111113E-3</v>
+        <v>6.0069444444444441E-3</v>
       </c>
       <c r="I100" s="1">
-        <v>46237.670601851853</v>
+        <v>46237.669907407406</v>
       </c>
       <c r="J100" s="2">
         <v>0</v>
@@ -3218,19 +3197,19 @@
         <v>27</v>
       </c>
       <c r="C101">
-        <v>5559</v>
+        <v>5558</v>
       </c>
       <c r="D101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F101" t="s">
         <v>24</v>
       </c>
       <c r="G101" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H101" s="2">
-        <v>1.1574074074074075E-4</v>
+        <v>8.9236111111111113E-3</v>
       </c>
       <c r="I101" s="1">
         <v>46237.670601851853</v>
@@ -3243,40 +3222,40 @@
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H102" s="2"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="2"/>
+      <c r="B102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102">
+        <v>5559</v>
+      </c>
+      <c r="D102" t="s">
+        <v>40</v>
+      </c>
+      <c r="F102" t="s">
+        <v>24</v>
+      </c>
+      <c r="G102" t="s">
+        <v>12</v>
+      </c>
+      <c r="H102" s="2">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="I102" s="1">
+        <v>46237.670601851853</v>
+      </c>
+      <c r="J102" s="2">
+        <v>3</v>
+      </c>
       <c r="K102" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H103" s="2"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>27</v>
-      </c>
-      <c r="C103">
-        <v>5932</v>
-      </c>
-      <c r="D103" t="s">
-        <v>50</v>
-      </c>
-      <c r="F103" t="s">
-        <v>24</v>
-      </c>
-      <c r="G103" t="s">
-        <v>10</v>
-      </c>
-      <c r="H103" s="2">
-        <v>8.2060185185185187E-3</v>
-      </c>
-      <c r="I103" s="1">
-        <v>46237.671296296299</v>
-      </c>
-      <c r="J103" s="2">
-        <v>0</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
@@ -3284,10 +3263,10 @@
         <v>27</v>
       </c>
       <c r="C104">
-        <v>5560</v>
+        <v>5932</v>
       </c>
       <c r="D104" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F104" t="s">
         <v>24</v>
@@ -3296,7 +3275,7 @@
         <v>10</v>
       </c>
       <c r="H104" s="2">
-        <v>6.7361111111111111E-3</v>
+        <v>8.2060185185185187E-3</v>
       </c>
       <c r="I104" s="1">
         <v>46237.671296296299</v>
@@ -3313,22 +3292,22 @@
         <v>27</v>
       </c>
       <c r="C105">
-        <v>5944</v>
+        <v>5560</v>
       </c>
       <c r="D105" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F105" t="s">
         <v>24</v>
       </c>
       <c r="G105" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H105" s="2">
-        <v>0</v>
+        <v>6.7361111111111111E-3</v>
       </c>
       <c r="I105" s="1">
-        <v>46237.671990740739</v>
+        <v>46237.671296296299</v>
       </c>
       <c r="J105" s="2">
         <v>0</v>
@@ -3342,10 +3321,10 @@
         <v>27</v>
       </c>
       <c r="C106">
-        <v>5561</v>
+        <v>5944</v>
       </c>
       <c r="D106" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F106" t="s">
         <v>24</v>
@@ -3357,10 +3336,10 @@
         <v>0</v>
       </c>
       <c r="I106" s="1">
-        <v>46237.672685185185</v>
+        <v>46237.671990740739</v>
       </c>
       <c r="J106" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K106" s="1" t="s">
         <v>11</v>
@@ -3371,10 +3350,10 @@
         <v>27</v>
       </c>
       <c r="C107">
-        <v>5563</v>
+        <v>5561</v>
       </c>
       <c r="D107" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F107" t="s">
         <v>24</v>
@@ -3383,13 +3362,13 @@
         <v>10</v>
       </c>
       <c r="H107" s="2">
-        <v>6.3078703703703708E-3</v>
+        <v>6.6435185185185182E-3</v>
       </c>
       <c r="I107" s="1">
         <v>46237.672685185185</v>
       </c>
       <c r="J107" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K107" s="1" t="s">
         <v>11</v>
@@ -3400,10 +3379,10 @@
         <v>27</v>
       </c>
       <c r="C108">
-        <v>5568</v>
+        <v>5563</v>
       </c>
       <c r="D108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F108" t="s">
         <v>24</v>
@@ -3412,10 +3391,10 @@
         <v>10</v>
       </c>
       <c r="H108" s="2">
-        <v>8.3564814814814821E-3</v>
+        <v>6.3078703703703708E-3</v>
       </c>
       <c r="I108" s="1">
-        <v>46237.673379629632</v>
+        <v>46237.672685185185</v>
       </c>
       <c r="J108" s="2">
         <v>0</v>
@@ -3429,22 +3408,22 @@
         <v>27</v>
       </c>
       <c r="C109">
-        <v>5566</v>
+        <v>5568</v>
       </c>
       <c r="D109" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F109" t="s">
         <v>24</v>
       </c>
       <c r="G109" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H109" s="2">
-        <v>0</v>
+        <v>8.3564814814814821E-3</v>
       </c>
       <c r="I109" s="1">
-        <v>46237.674074074072</v>
+        <v>46237.673379629632</v>
       </c>
       <c r="J109" s="2">
         <v>0</v>
@@ -3454,47 +3433,70 @@
       </c>
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H110" s="2"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="2"/>
+      <c r="B110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110">
+        <v>5566</v>
+      </c>
+      <c r="D110" t="s">
+        <v>45</v>
+      </c>
+      <c r="F110" t="s">
+        <v>24</v>
+      </c>
+      <c r="G110" t="s">
+        <v>12</v>
+      </c>
+      <c r="H110" s="2">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="I110" s="1">
+        <v>46237.674074074072</v>
+      </c>
+      <c r="J110" s="2">
+        <v>3</v>
+      </c>
       <c r="K110" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H111" s="2"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B111" t="s">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
         <v>27</v>
       </c>
-      <c r="C111">
+      <c r="C112">
         <v>5565</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D112" t="s">
         <v>46</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F112" t="s">
         <v>24</v>
       </c>
-      <c r="G111" t="s">
+      <c r="G112" t="s">
         <v>10</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H112" s="2">
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="I111" s="1">
+      <c r="I112" s="1">
         <v>46237.674074074072</v>
       </c>
-      <c r="J111" s="2">
+      <c r="J112" s="2">
         <v>0</v>
       </c>
-      <c r="K111" s="1" t="s">
+      <c r="K112" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H112" s="2"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="2"/>
-      <c r="K112" s="1"/>
     </row>
     <row r="113" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H113" s="2"/>
@@ -3508,7 +3510,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -3580,7 +3582,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -3862,7 +3864,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -3892,7 +3894,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -3952,7 +3954,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -4060,7 +4062,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -4252,7 +4254,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -4768,7 +4770,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -4834,7 +4836,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -4846,7 +4848,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -4942,7 +4944,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -4954,7 +4956,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -5050,7 +5052,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -5110,7 +5112,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -44063,6 +44065,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -44355,6 +44358,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -44665,6 +44670,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -44789,6 +44795,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -44800,6 +44807,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -44948,6 +44956,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -44958,10 +44967,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -44995,15 +45006,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -45044,18 +45058,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -45071,6 +45089,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -45080,10 +45099,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -45119,10 +45140,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -45148,6 +45171,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -45162,6 +45186,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -45196,6 +45221,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -45205,6 +45231,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -45214,6 +45241,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -45228,15 +45256,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -45266,6 +45295,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -45286,11 +45316,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -45299,6 +45331,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -45328,6 +45361,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -45337,10 +45371,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -45355,14 +45391,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -45382,10 +45421,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -45405,9 +45446,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -45442,18 +45486,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -45468,12 +45516,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -45488,10 +45536,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -45511,6 +45561,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -45530,6 +45581,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -45539,6 +45591,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -45584,6 +45637,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -45593,6 +45647,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -45607,6 +45662,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -45616,10 +45672,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -45634,6 +45692,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -45643,6 +45702,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -45662,6 +45722,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -45681,10 +45742,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -45694,6 +45757,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -45704,10 +45768,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -45722,18 +45788,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -45753,10 +45823,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -45776,6 +45848,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -45806,7 +45879,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -45821,10 +45893,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -45839,6 +45913,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -45853,11 +45928,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -45867,6 +45942,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -45882,6 +45958,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -45896,6 +45973,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -45916,6 +45994,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -45941,11 +46020,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -45964,15 +46045,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -45982,6 +46064,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -46001,6 +46084,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -46015,6 +46099,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -46034,10 +46119,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -46047,6 +46134,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -46057,6 +46145,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -46093,7 +46182,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -46102,6 +46190,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -46115,10 +46204,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Brads-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03D275F3-7476-4CF2-B83D-FD5AC0CF6590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29A2C969-C7F4-4D19-BD31-FA698F7CFBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -644,7 +644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>27</v>
       </c>
@@ -797,7 +797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -892,7 +892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1359,7 +1359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>27</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>27</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>27</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>27</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -2973,7 +2973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>27</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>27</v>
       </c>
@@ -3510,7 +3510,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -3582,7 +3582,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -3864,7 +3864,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -3894,7 +3894,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -3954,7 +3954,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -4062,7 +4062,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -4254,7 +4254,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -4770,7 +4770,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -4836,7 +4836,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -4848,7 +4848,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -4944,7 +4944,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -4956,7 +4956,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -5052,7 +5052,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -5112,7 +5112,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -44065,7 +44065,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -44358,8 +44357,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -44670,7 +44667,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -44795,7 +44791,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -44807,7 +44802,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -44956,35 +44950,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -44995,44 +44983,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -45043,37 +45022,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -45084,52 +45056,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -45140,17 +45102,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -45161,32 +45120,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -45196,106 +45149,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -45305,7 +45238,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -45316,127 +45248,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -45446,62 +45352,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -45521,67 +45414,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -45591,38 +45471,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -45637,117 +45510,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -45756,99 +45606,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -45858,23 +45689,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -45883,52 +45710,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -45942,38 +45759,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -45983,7 +45793,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -45994,23 +45803,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -46020,37 +45825,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -46059,72 +45857,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -46134,76 +45918,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
